--- a/data/sources/countries/trinidad_and_tobago.xlsx
+++ b/data/sources/countries/trinidad_and_tobago.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,23 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="9"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F3864"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -58,9 +48,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,377 +414,293 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI52"/>
+  <dimension ref="A1:BE52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="38" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="70" customWidth="1" min="16" max="16"/>
-    <col width="70" customWidth="1" min="17" max="17"/>
-    <col width="26" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
-    <col width="14" customWidth="1" min="25" max="25"/>
-    <col width="14" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
-    <col width="14" customWidth="1" min="29" max="29"/>
-    <col width="14" customWidth="1" min="30" max="30"/>
-    <col width="14" customWidth="1" min="31" max="31"/>
-    <col width="14" customWidth="1" min="32" max="32"/>
-    <col width="14" customWidth="1" min="33" max="33"/>
-    <col width="14" customWidth="1" min="34" max="34"/>
-    <col width="14" customWidth="1" min="35" max="35"/>
-    <col width="14" customWidth="1" min="36" max="36"/>
-    <col width="14" customWidth="1" min="37" max="37"/>
-    <col width="14" customWidth="1" min="38" max="38"/>
-    <col width="14" customWidth="1" min="39" max="39"/>
-    <col width="14" customWidth="1" min="40" max="40"/>
-    <col width="14" customWidth="1" min="41" max="41"/>
-    <col width="14" customWidth="1" min="42" max="42"/>
-    <col width="14" customWidth="1" min="43" max="43"/>
-    <col width="14" customWidth="1" min="44" max="44"/>
-    <col width="14" customWidth="1" min="45" max="45"/>
-    <col width="14" customWidth="1" min="46" max="46"/>
-    <col width="14" customWidth="1" min="47" max="47"/>
-    <col width="14" customWidth="1" min="48" max="48"/>
-    <col width="14" customWidth="1" min="49" max="49"/>
-    <col width="14" customWidth="1" min="50" max="50"/>
-    <col width="14" customWidth="1" min="51" max="51"/>
-    <col width="14" customWidth="1" min="52" max="52"/>
-    <col width="14" customWidth="1" min="53" max="53"/>
-    <col width="14" customWidth="1" min="54" max="54"/>
-    <col width="80" customWidth="1" min="55" max="55"/>
-    <col width="14" customWidth="1" min="56" max="56"/>
-    <col width="26" customWidth="1" min="57" max="57"/>
-    <col width="14" customWidth="1" min="58" max="58"/>
-    <col width="14" customWidth="1" min="59" max="59"/>
-    <col width="14" customWidth="1" min="60" max="60"/>
-    <col width="14" customWidth="1" min="61" max="61"/>
-    <col width="14" customWidth="1" min="62" max="62"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Id_Investment</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Id_Investment_Original</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Id_Seq</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Coordinates</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>COUNTRY_ISO_ALPHA3</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>COUNTRY_ISO_NUM</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Province_ISO</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Investor</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Vector</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Path</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Area_EN</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Area_ES</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Detail_ES</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Detail_EN</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Investment</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Joint_Venture</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Origin_Of_Seller</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Stake</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Project_Type</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>News</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Caso1</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Link1</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Caso2</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Link2</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Caso3</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Link3</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Caso4</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Link4</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Caso5</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Link5</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Caso6</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Link6</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Caso7</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Link7</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>Caso8</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Link8</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Caso9</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Link9</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>Caso10</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>Link10</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>Caso11</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>Link11</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Caso12</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>Link12</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>Caso13</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>Link13</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>Caso14</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>Link14</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>reliability_score</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>reliability_notes</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>cancelled</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>cancelled_motivo</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>source1</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>source2</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>source3</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>source4</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>source5</t>
         </is>
       </c>
     </row>
@@ -824,14 +728,9 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>780</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>N/A</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -839,7 +738,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>China National Offshore Oil Corporation and Sinopec</t>
+          <t>Chaoyang Petroleum (BVI) Ltd. -- JV 50:50 CNOOC / Sinopec</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -904,20 +803,20 @@
       <c r="BA2" t="n">
         <v>3</v>
       </c>
-      <c r="BC2" t="n">
+      <c r="BB2" t="n">
         <v>0</v>
       </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/0001095595/000095010309001714/dp14160_6k.htm</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/0001095595/000095010310001157/dp17202_ex1502.htm</t>
+        </is>
+      </c>
       <c r="BE2" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0001095595/000095010309001714/dp14160_6k.htm</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0001095595/000095010310001157/dp17202_ex1502.htm</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
         <is>
           <t>https://www.guardian.co.tt/article-6.2.450605.98b132e9ca</t>
         </is>
@@ -947,7 +846,7 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>780</t>
         </is>
@@ -962,7 +861,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>China Railway Construction Corporation</t>
+          <t>China Railway Construction Corp. (CRCC)</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1019,20 +918,20 @@
       <c r="BA3" t="n">
         <v>3</v>
       </c>
-      <c r="BC3" t="n">
+      <c r="BB3" t="n">
         <v>0</v>
       </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>https://www.guardian.co.tt/article-6.2.408731.3817c8f714</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>https://www.globalconstructionreview.com/chinese-firms-fund-and-build-160m-hospital-trinida</t>
+        </is>
+      </c>
       <c r="BE3" t="inlineStr">
-        <is>
-          <t>https://www.guardian.co.tt/article-6.2.408731.3817c8f714</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>https://www.globalconstructionreview.com/chinese-firms-fund-and-build-160m-hospital-trinida</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
         <is>
           <t>https://newsday.co.tt/2019/03/07/china-railways-road-in-tt/</t>
         </is>
@@ -1062,7 +961,7 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>780</t>
         </is>
@@ -1131,20 +1030,20 @@
       <c r="BA4" t="n">
         <v>3</v>
       </c>
-      <c r="BC4" t="n">
+      <c r="BB4" t="n">
         <v>0</v>
       </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>https://trinidadexpress.com/news/local/from-shanghai-to-trinidad/article_d4507526-0182-55f7-89d1-cfde43c8bf74.html</t>
+        </is>
+      </c>
       <c r="BE4" t="inlineStr">
-        <is>
-          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>https://trinidadexpress.com/news/local/from-shanghai-to-trinidad/article_d4507526-0182-55f7-89d1-cfde43c8bf74.html</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
         <is>
           <t>https://globalamericans.org/chinas-engagement-with-trinidad-and-tobago/</t>
         </is>
@@ -1174,7 +1073,7 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>780</t>
         </is>
@@ -1246,20 +1145,20 @@
       <c r="BA5" t="n">
         <v>3</v>
       </c>
-      <c r="BC5" t="n">
+      <c r="BB5" t="n">
         <v>0</v>
       </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>https://universalprojectsltd.com/wordpress/aquatic-center/</t>
+        </is>
+      </c>
       <c r="BE5" t="inlineStr">
-        <is>
-          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>https://universalprojectsltd.com/wordpress/aquatic-center/</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
         <is>
           <t>https://sportt-tt.com/book-a-facility/national-aquatic-centre/</t>
         </is>
@@ -1289,7 +1188,7 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="1" t="inlineStr">
         <is>
           <t>780</t>
         </is>
@@ -1304,7 +1203,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Sinohydro Corporation Ltd. / PowerChina</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1361,20 +1260,20 @@
       <c r="BA6" t="n">
         <v>4</v>
       </c>
-      <c r="BC6" t="n">
+      <c r="BB6" t="n">
         <v>0</v>
       </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>https://en.powerchina.cn/2019-07/19/c_714119.htm</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>https://archives.newsday.co.tt/2015/04/30/chinese-to-build-620m-wastewater-plant/</t>
+        </is>
+      </c>
       <c r="BE6" t="inlineStr">
-        <is>
-          <t>https://en.powerchina.cn/2019-07/19/c_714119.htm</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>https://archives.newsday.co.tt/2015/04/30/chinese-to-build-620m-wastewater-plant/</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
         <is>
           <t>https://archives.newsday.co.tt/2014/11/18/us579-million-to-build-wastewater-plants/</t>
         </is>
@@ -1404,7 +1303,7 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="1" t="inlineStr">
         <is>
           <t>780</t>
         </is>
@@ -1419,7 +1318,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Beijing Construction Engineering Group</t>
+          <t>Beijing Construction Engineering Group (BCEG)</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1476,20 +1375,20 @@
       <c r="BA7" t="n">
         <v>4</v>
       </c>
-      <c r="BC7" t="n">
+      <c r="BB7" t="n">
         <v>0</v>
       </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>https://trinidadexpress.com/business/local/china-to-fund-phoenix-park-industrial-estate/article_31be9880-7498-11e8-aa35-134f694d9978.html</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>https://eteck.co.tt/index.php/2018/06/21/684/</t>
+        </is>
+      </c>
       <c r="BE7" t="inlineStr">
-        <is>
-          <t>https://trinidadexpress.com/business/local/china-to-fund-phoenix-park-industrial-estate/article_31be9880-7498-11e8-aa35-134f694d9978.html</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>https://eteck.co.tt/index.php/2018/06/21/684/</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
         <is>
           <t>https://tradeind.gov.tt/chinese_firms_invest_phoenix_industrial_estate/</t>
         </is>
@@ -1519,7 +1418,7 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="1" t="inlineStr">
         <is>
           <t>780</t>
         </is>
@@ -1591,15 +1490,15 @@
       <c r="BA8" t="n">
         <v>4</v>
       </c>
-      <c r="BC8" t="n">
+      <c r="BB8" t="n">
         <v>0</v>
       </c>
-      <c r="BE8" t="inlineStr">
+      <c r="BC8" t="inlineStr">
         <is>
           <t>https://www.globalconstructionreview.com/chinese-firms-fund-and-build-160m-hospital-trinida</t>
         </is>
       </c>
-      <c r="BF8" t="inlineStr">
+      <c r="BD8" t="inlineStr">
         <is>
           <t>https://www.globenewswire.com/news-release/2024/07/17/2914346/0/en/CRCC-Spearheading-the-Modernization-of-Port-of-Spain-General-Hospital.html</t>
         </is>
@@ -1629,7 +1528,7 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="1" t="inlineStr">
         <is>
           <t>780</t>
         </is>
@@ -1644,7 +1543,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Summit Luggage</t>
+          <t>Summit Luggage Co., Ltd.</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1698,20 +1597,20 @@
       <c r="BA9" t="n">
         <v>4</v>
       </c>
-      <c r="BC9" t="n">
+      <c r="BB9" t="n">
         <v>0</v>
       </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>https://businessfacilities.com/two-china-based-companies-choose-trinidad-and-tobago-location</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>https://tradeind.gov.tt/chinese_firms_invest_phoenix_industrial_estate/</t>
+        </is>
+      </c>
       <c r="BE9" t="inlineStr">
-        <is>
-          <t>https://businessfacilities.com/two-china-based-companies-choose-trinidad-and-tobago-location</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>https://tradeind.gov.tt/chinese_firms_invest_phoenix_industrial_estate/</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
         <is>
           <t>http://www.china.org.cn/world/Off_the_Wire/2023-09/23/content_116705829.htm</t>
         </is>
@@ -1741,14 +1640,9 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="1" t="inlineStr">
         <is>
           <t>780</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>N/A</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -1756,7 +1650,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>China National Offshore Oil Corporation</t>
+          <t>CNOOC International (China National Offshore Oil Corporation)</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1810,20 +1704,20 @@
       <c r="BA10" t="n">
         <v>4</v>
       </c>
-      <c r="BC10" t="n">
+      <c r="BB10" t="n">
         <v>0</v>
       </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>https://www.guardian.co.tt/business/tt-awards-two-offshore-blocks-to-chinese-state-company-6.2.2531632.001835bac9</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>https://oilnow.gy/news/chinese-oil-giant-leads-interest-in-trinidad-deepwater-blocks/</t>
+        </is>
+      </c>
       <c r="BE10" t="inlineStr">
-        <is>
-          <t>https://www.guardian.co.tt/business/tt-awards-two-offshore-blocks-to-chinese-state-company-6.2.2531632.001835bac9</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>https://oilnow.gy/news/chinese-oil-giant-leads-interest-in-trinidad-deepwater-blocks/</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
         <is>
           <t>https://www.energy.gov.tt/trinidad-and-tobago-welcomes-new-entrants-to-its-deep-water-frontier/</t>
         </is>
@@ -1853,7 +1747,7 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="1" t="inlineStr">
         <is>
           <t>780</t>
         </is>
@@ -1925,20 +1819,20 @@
       <c r="BA11" t="n">
         <v>5</v>
       </c>
-      <c r="BC11" t="n">
+      <c r="BB11" t="n">
         <v>0</v>
       </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>https://mowt.gov.tt/Divisions/Highways-Division/Projects/The-Curepe-Interchange-Project</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>https://newsday.co.tt/2019/03/07/china-railways-road-in-tt/</t>
+        </is>
+      </c>
       <c r="BE11" t="inlineStr">
-        <is>
-          <t>https://mowt.gov.tt/Divisions/Highways-Division/Projects/The-Curepe-Interchange-Project</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>https://newsday.co.tt/2019/03/07/china-railways-road-in-tt/</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
         <is>
           <t>https://eng.yidaiyilu.gov.cn/p/290666.html</t>
         </is>
@@ -1968,7 +1862,7 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="1" t="inlineStr">
         <is>
           <t>780</t>
         </is>
@@ -1983,7 +1877,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>China Railway Construction Corporation</t>
+          <t>China Railway Construction (Caribbean) Company Ltd.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -2040,20 +1934,20 @@
       <c r="BA12" t="n">
         <v>5</v>
       </c>
-      <c r="BC12" t="n">
+      <c r="BB12" t="n">
         <v>0</v>
       </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>https://www.airport-technology.com/projects/anr-robinson-international-airport-expansion-project/</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>https://newsday.co.tt/2025/08/16/no-date-set-for-opening-of-anr-robinson-airport/</t>
+        </is>
+      </c>
       <c r="BE12" t="inlineStr">
-        <is>
-          <t>https://www.airport-technology.com/projects/anr-robinson-international-airport-expansion-project/</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>https://newsday.co.tt/2025/08/16/no-date-set-for-opening-of-anr-robinson-airport/</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
         <is>
           <t>https://trinidadexpress.com/newsextra/chinese-company-to-resume-construction-of-airport-terminal-in-tobago/article_41438dcc-dc2a-11eb-8c53-df98c00fb914.html</t>
         </is>
@@ -2083,7 +1977,7 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="1" t="inlineStr">
         <is>
           <t>780</t>
         </is>
@@ -2098,7 +1992,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>China Investment Corporation</t>
+          <t>China Investment Corporation (CIC)</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -2163,25 +2057,20 @@
       <c r="BA13" t="n">
         <v>4</v>
       </c>
-      <c r="BC13" t="n">
-        <v>1</v>
+      <c r="BB13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>https://www.hartenergy.com/news/chinese-firm-takes-over-share-atlantic-lng-91768</t>
+        </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
-        <is>
-          <t>https://www.hartenergy.com/news/chinese-firm-takes-over-share-atlantic-lng-91768</t>
-        </is>
-      </c>
-      <c r="BF13" t="inlineStr">
-        <is>
-          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr">
         <is>
           <t>https://www.guardian.co.tt/article-6.2.448448.b331a5af49</t>
         </is>
@@ -2211,7 +2100,7 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="1" t="inlineStr">
         <is>
           <t>780</t>
         </is>
@@ -2283,25 +2172,20 @@
       <c r="BA14" t="n">
         <v>4</v>
       </c>
-      <c r="BC14" t="n">
-        <v>1</v>
+      <c r="BB14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>https://udecott.com/projects/the-couva-childrens-hospital-and-multi-training-facility/</t>
+        </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://www.cnc3.co.tt/hospital-on-hold/</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
-        <is>
-          <t>https://udecott.com/projects/the-couva-childrens-hospital-and-multi-training-facility/</t>
-        </is>
-      </c>
-      <c r="BF14" t="inlineStr">
-        <is>
-          <t>https://www.cnc3.co.tt/hospital-on-hold/</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr">
         <is>
           <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
         </is>
@@ -2331,7 +2215,7 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="1" t="inlineStr">
         <is>
           <t>780</t>
         </is>
@@ -2346,7 +2230,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Gezhouba</t>
+          <t>China Gezhouba Group International</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2403,25 +2287,20 @@
       <c r="BA15" t="n">
         <v>1</v>
       </c>
-      <c r="BC15" t="n">
-        <v>1</v>
+      <c r="BB15" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>https://newsday.co.tt/2021/12/20/a-dry-dock-comes-to-la-brea/</t>
+        </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/La-Brea-Dry-Docking-Facility</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
-        <is>
-          <t>https://newsday.co.tt/2021/12/20/a-dry-dock-comes-to-la-brea/</t>
-        </is>
-      </c>
-      <c r="BF15" t="inlineStr">
-        <is>
-          <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/La-Brea-Dry-Docking-Facility</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr">
         <is>
           <t>https://www.cijn.org/chinas-opaque-caribbean-trail-dreams-deals-and-debt/</t>
         </is>
@@ -2451,7 +2330,7 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" s="1" t="inlineStr">
         <is>
           <t>780</t>
         </is>
@@ -2520,20 +2399,15 @@
       <c r="BA16" t="n">
         <v>2</v>
       </c>
-      <c r="BC16" t="n">
-        <v>1</v>
+      <c r="BB16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
+        </is>
       </c>
       <c r="BD16" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE16" t="inlineStr">
-        <is>
-          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
-        </is>
-      </c>
-      <c r="BF16" t="inlineStr">
         <is>
           <t>https://econvue.com/pulse/china%E2%80%99s-engagement-trinidad-and-tobago</t>
         </is>
@@ -2563,7 +2437,7 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" s="1" t="inlineStr">
         <is>
           <t>780</t>
         </is>
@@ -2578,7 +2452,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>China Railway Construction Corporation</t>
+          <t>China Railway Construction Corporation (CRCC)</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2601,12 +2475,22 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
+          <t>Carretera de Valencia a Toco y puerto de ferry de Toco</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
           <t>Valencia to Toco roadway and Toco ferry port</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>SAN JUAN-LAVENTILLE</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Construcción</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -2622,20 +2506,15 @@
       <c r="BA17" t="n">
         <v>2</v>
       </c>
-      <c r="BC17" t="n">
-        <v>1</v>
+      <c r="BB17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
+        </is>
       </c>
       <c r="BD17" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE17" t="inlineStr">
-        <is>
-          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
-        </is>
-      </c>
-      <c r="BF17" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
@@ -2665,7 +2544,7 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" s="1" t="inlineStr">
         <is>
           <t>780</t>
         </is>
@@ -2680,7 +2559,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>China Railway Construction Corporation</t>
+          <t>China Railway Construction Corporation (CRCC)</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2703,12 +2582,22 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
+          <t>Carretera de Valencia a Toco y puerto de ferry de Toco</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
           <t>Valencia to Toco roadway and Toco ferry port</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
           <t>SAN JUAN-LAVENTILLE</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Construcción</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -2724,20 +2613,15 @@
       <c r="BA18" t="n">
         <v>2</v>
       </c>
-      <c r="BC18" t="n">
-        <v>1</v>
+      <c r="BB18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
+        </is>
       </c>
       <c r="BD18" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE18" t="inlineStr">
-        <is>
-          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
-        </is>
-      </c>
-      <c r="BF18" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
@@ -2767,7 +2651,7 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" s="1" t="inlineStr">
         <is>
           <t>780</t>
         </is>
@@ -2782,7 +2666,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>China Railway Construction Corporation</t>
+          <t>China Railway Construction Corporation (CRCC)</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2805,12 +2689,22 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
+          <t>Carretera de Valencia a Toco y puerto de ferry de Toco</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
           <t>Valencia to Toco roadway and Toco ferry port</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
           <t>SAN JUAN-LAVENTILLE</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Construcción</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -2826,20 +2720,15 @@
       <c r="BA19" t="n">
         <v>2</v>
       </c>
-      <c r="BC19" t="n">
-        <v>1</v>
+      <c r="BB19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
+        </is>
       </c>
       <c r="BD19" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE19" t="inlineStr">
-        <is>
-          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
-        </is>
-      </c>
-      <c r="BF19" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
@@ -2869,7 +2758,7 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="1" t="inlineStr">
         <is>
           <t>780</t>
         </is>
@@ -2884,7 +2773,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>China Railway Construction Corporation</t>
+          <t>China Railway Construction Corporation (CRCC)</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2907,12 +2796,22 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
+          <t>Carretera de Valencia a Toco y puerto de ferry de Toco</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
           <t>Valencia to Toco roadway and Toco ferry port</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
           <t>SAN JUAN-LAVENTILLE</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Construcción</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -2928,20 +2827,15 @@
       <c r="BA20" t="n">
         <v>2</v>
       </c>
-      <c r="BC20" t="n">
-        <v>1</v>
+      <c r="BB20" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
+        </is>
       </c>
       <c r="BD20" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE20" t="inlineStr">
-        <is>
-          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
-        </is>
-      </c>
-      <c r="BF20" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
@@ -2971,7 +2865,7 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" s="1" t="inlineStr">
         <is>
           <t>780</t>
         </is>
@@ -2986,7 +2880,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>China Railway Construction Corporation</t>
+          <t>China Railway Construction Corporation (CRCC)</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3009,12 +2903,22 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
+          <t>Carretera de Valencia a Toco y puerto de ferry de Toco</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
           <t>Valencia to Toco roadway and Toco ferry port</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
           <t>SAN JUAN-LAVENTILLE</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Construcción</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -3030,20 +2934,15 @@
       <c r="BA21" t="n">
         <v>2</v>
       </c>
-      <c r="BC21" t="n">
-        <v>1</v>
+      <c r="BB21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
+        </is>
       </c>
       <c r="BD21" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE21" t="inlineStr">
-        <is>
-          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
-        </is>
-      </c>
-      <c r="BF21" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
@@ -3073,7 +2972,7 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" s="1" t="inlineStr">
         <is>
           <t>780</t>
         </is>
@@ -3088,7 +2987,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>China Railway Construction Corporation</t>
+          <t>China Railway Construction Corporation (CRCC)</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3111,12 +3010,22 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
+          <t>Carretera de Valencia a Toco y puerto de ferry de Toco</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
           <t>Valencia to Toco roadway and Toco ferry port</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
           <t>TUNAPUNA/PIARCO</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Construcción</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -3132,20 +3041,15 @@
       <c r="BA22" t="n">
         <v>2</v>
       </c>
-      <c r="BC22" t="n">
-        <v>1</v>
+      <c r="BB22" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
+        </is>
       </c>
       <c r="BD22" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE22" t="inlineStr">
-        <is>
-          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
-        </is>
-      </c>
-      <c r="BF22" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
@@ -3175,7 +3079,7 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" s="1" t="inlineStr">
         <is>
           <t>780</t>
         </is>
@@ -3190,7 +3094,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>China Railway Construction Corporation</t>
+          <t>China Railway Construction Corporation (CRCC)</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -3213,12 +3117,22 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
+          <t>Carretera de Valencia a Toco y puerto de ferry de Toco</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
           <t>Valencia to Toco roadway and Toco ferry port</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
           <t>TUNAPUNA/PIARCO</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Construcción</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -3234,20 +3148,15 @@
       <c r="BA23" t="n">
         <v>2</v>
       </c>
-      <c r="BC23" t="n">
-        <v>1</v>
+      <c r="BB23" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
+        </is>
       </c>
       <c r="BD23" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE23" t="inlineStr">
-        <is>
-          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
-        </is>
-      </c>
-      <c r="BF23" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
@@ -3277,7 +3186,7 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" s="1" t="inlineStr">
         <is>
           <t>780</t>
         </is>
@@ -3292,7 +3201,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>China Railway Construction Corporation</t>
+          <t>China Railway Construction Corporation (CRCC)</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3315,12 +3224,22 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
+          <t>Carretera de Valencia a Toco y puerto de ferry de Toco</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
           <t>Valencia to Toco roadway and Toco ferry port</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
           <t>TUNAPUNA/PIARCO</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Construcción</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -3336,20 +3255,15 @@
       <c r="BA24" t="n">
         <v>2</v>
       </c>
-      <c r="BC24" t="n">
-        <v>1</v>
+      <c r="BB24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC24" t="inlineStr">
+        <is>
+          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
+        </is>
       </c>
       <c r="BD24" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE24" t="inlineStr">
-        <is>
-          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
-        </is>
-      </c>
-      <c r="BF24" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
@@ -3379,7 +3293,7 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" s="1" t="inlineStr">
         <is>
           <t>780</t>
         </is>
@@ -3394,7 +3308,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>China Railway Construction Corporation</t>
+          <t>China Railway Construction Corporation (CRCC)</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -3417,12 +3331,22 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
+          <t>Carretera de Valencia a Toco y puerto de ferry de Toco</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
           <t>Valencia to Toco roadway and Toco ferry port</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
           <t>TUNAPUNA/PIARCO</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Construcción</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3438,20 +3362,15 @@
       <c r="BA25" t="n">
         <v>2</v>
       </c>
-      <c r="BC25" t="n">
-        <v>1</v>
+      <c r="BB25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC25" t="inlineStr">
+        <is>
+          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
+        </is>
       </c>
       <c r="BD25" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE25" t="inlineStr">
-        <is>
-          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
-        </is>
-      </c>
-      <c r="BF25" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
@@ -3481,7 +3400,7 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" s="1" t="inlineStr">
         <is>
           <t>780</t>
         </is>
@@ -3496,7 +3415,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>China Railway Construction Corporation</t>
+          <t>China Railway Construction Corporation (CRCC)</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3519,12 +3438,22 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
+          <t>Carretera de Valencia a Toco y puerto de ferry de Toco</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
           <t>Valencia to Toco roadway and Toco ferry port</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
           <t>SAN JUAN-LAVENTILLE</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Construcción</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -3540,20 +3469,15 @@
       <c r="BA26" t="n">
         <v>2</v>
       </c>
-      <c r="BC26" t="n">
-        <v>1</v>
+      <c r="BB26" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC26" t="inlineStr">
+        <is>
+          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
+        </is>
       </c>
       <c r="BD26" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE26" t="inlineStr">
-        <is>
-          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
-        </is>
-      </c>
-      <c r="BF26" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
@@ -3583,7 +3507,7 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" s="1" t="inlineStr">
         <is>
           <t>780</t>
         </is>
@@ -3598,7 +3522,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>China Railway Construction Corporation</t>
+          <t>China Railway Construction Corporation (CRCC)</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3621,12 +3545,22 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
+          <t>Carretera de Valencia a Toco y puerto de ferry de Toco</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
           <t>Valencia to Toco roadway and Toco ferry port</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
           <t>TUNAPUNA/PIARCO</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Construcción</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -3642,20 +3576,15 @@
       <c r="BA27" t="n">
         <v>2</v>
       </c>
-      <c r="BC27" t="n">
-        <v>1</v>
+      <c r="BB27" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC27" t="inlineStr">
+        <is>
+          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
+        </is>
       </c>
       <c r="BD27" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE27" t="inlineStr">
-        <is>
-          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
-        </is>
-      </c>
-      <c r="BF27" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
@@ -3685,7 +3614,7 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" s="1" t="inlineStr">
         <is>
           <t>780</t>
         </is>
@@ -3700,7 +3629,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>China Railway Construction Corporation</t>
+          <t>China Railway Construction Corporation (CRCC)</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3723,12 +3652,22 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
+          <t>Carretera de Valencia a Toco y puerto de ferry de Toco</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
           <t>Valencia to Toco roadway and Toco ferry port</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
           <t>TUNAPUNA/PIARCO</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Construcción</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -3744,20 +3683,15 @@
       <c r="BA28" t="n">
         <v>2</v>
       </c>
-      <c r="BC28" t="n">
-        <v>1</v>
+      <c r="BB28" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC28" t="inlineStr">
+        <is>
+          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
+        </is>
       </c>
       <c r="BD28" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE28" t="inlineStr">
-        <is>
-          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
-        </is>
-      </c>
-      <c r="BF28" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
@@ -3787,7 +3721,7 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G29" s="1" t="inlineStr">
         <is>
           <t>780</t>
         </is>
@@ -3802,7 +3736,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>China Railway Construction Corporation</t>
+          <t>China Railway Construction Corporation (CRCC)</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3825,12 +3759,22 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
+          <t>Carretera de Valencia a Toco y puerto de ferry de Toco</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
           <t>Valencia to Toco roadway and Toco ferry port</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
           <t>TUNAPUNA/PIARCO</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Construcción</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -3846,20 +3790,15 @@
       <c r="BA29" t="n">
         <v>2</v>
       </c>
-      <c r="BC29" t="n">
-        <v>1</v>
+      <c r="BB29" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC29" t="inlineStr">
+        <is>
+          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
+        </is>
       </c>
       <c r="BD29" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE29" t="inlineStr">
-        <is>
-          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
-        </is>
-      </c>
-      <c r="BF29" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
@@ -3889,7 +3828,7 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G30" s="1" t="inlineStr">
         <is>
           <t>780</t>
         </is>
@@ -3904,7 +3843,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>China Railway Construction Corporation</t>
+          <t>China Railway Construction Corporation (CRCC)</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3927,12 +3866,22 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
+          <t>Carretera de Valencia a Toco y puerto de ferry de Toco</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
           <t>Valencia to Toco roadway and Toco ferry port</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
           <t>TUNAPUNA/PIARCO</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Construcción</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
@@ -3948,20 +3897,15 @@
       <c r="BA30" t="n">
         <v>2</v>
       </c>
-      <c r="BC30" t="n">
-        <v>1</v>
+      <c r="BB30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC30" t="inlineStr">
+        <is>
+          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
+        </is>
       </c>
       <c r="BD30" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE30" t="inlineStr">
-        <is>
-          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
-        </is>
-      </c>
-      <c r="BF30" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
@@ -3991,7 +3935,7 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G31" s="1" t="inlineStr">
         <is>
           <t>780</t>
         </is>
@@ -4006,7 +3950,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>China Railway Construction Corporation</t>
+          <t>China Railway Construction Corporation (CRCC)</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -4029,12 +3973,22 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
+          <t>Carretera de Valencia a Toco y puerto de ferry de Toco</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
           <t>Valencia to Toco roadway and Toco ferry port</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
           <t>TUNAPUNA/PIARCO</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Construcción</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -4050,20 +4004,15 @@
       <c r="BA31" t="n">
         <v>2</v>
       </c>
-      <c r="BC31" t="n">
-        <v>1</v>
+      <c r="BB31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC31" t="inlineStr">
+        <is>
+          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
+        </is>
       </c>
       <c r="BD31" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE31" t="inlineStr">
-        <is>
-          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
-        </is>
-      </c>
-      <c r="BF31" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
@@ -4093,7 +4042,7 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" s="1" t="inlineStr">
         <is>
           <t>780</t>
         </is>
@@ -4108,7 +4057,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>China Railway Construction Corporation</t>
+          <t>China Railway Construction Corporation (CRCC)</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -4131,12 +4080,22 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
+          <t>Carretera de Valencia a Toco y puerto de ferry de Toco</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
           <t>Valencia to Toco roadway and Toco ferry port</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
           <t>TUNAPUNA/PIARCO</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Construcción</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
@@ -4152,20 +4111,15 @@
       <c r="BA32" t="n">
         <v>2</v>
       </c>
-      <c r="BC32" t="n">
-        <v>1</v>
+      <c r="BB32" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC32" t="inlineStr">
+        <is>
+          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
+        </is>
       </c>
       <c r="BD32" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE32" t="inlineStr">
-        <is>
-          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
-        </is>
-      </c>
-      <c r="BF32" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
@@ -4195,7 +4149,7 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" s="1" t="inlineStr">
         <is>
           <t>780</t>
         </is>
@@ -4210,7 +4164,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>China Railway Construction Corporation</t>
+          <t>China Railway Construction Corporation (CRCC)</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -4233,12 +4187,22 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
+          <t>Carretera de Valencia a Toco y puerto de ferry de Toco</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
           <t>Valencia to Toco roadway and Toco ferry port</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
           <t>TUNAPUNA/PIARCO</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Construcción</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
@@ -4254,20 +4218,15 @@
       <c r="BA33" t="n">
         <v>2</v>
       </c>
-      <c r="BC33" t="n">
-        <v>1</v>
+      <c r="BB33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC33" t="inlineStr">
+        <is>
+          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
+        </is>
       </c>
       <c r="BD33" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE33" t="inlineStr">
-        <is>
-          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
-        </is>
-      </c>
-      <c r="BF33" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
@@ -4297,7 +4256,7 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" s="1" t="inlineStr">
         <is>
           <t>780</t>
         </is>
@@ -4312,7 +4271,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>China Railway Construction Corporation</t>
+          <t>China Railway Construction Corporation (CRCC)</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -4335,12 +4294,22 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
+          <t>Carretera de Valencia a Toco y puerto de ferry de Toco</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
           <t>Valencia to Toco roadway and Toco ferry port</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
           <t>TUNAPUNA/PIARCO</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Construcción</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
@@ -4356,20 +4325,15 @@
       <c r="BA34" t="n">
         <v>2</v>
       </c>
-      <c r="BC34" t="n">
-        <v>1</v>
+      <c r="BB34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC34" t="inlineStr">
+        <is>
+          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
+        </is>
       </c>
       <c r="BD34" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE34" t="inlineStr">
-        <is>
-          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
-        </is>
-      </c>
-      <c r="BF34" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
@@ -4399,7 +4363,7 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G35" s="1" t="inlineStr">
         <is>
           <t>780</t>
         </is>
@@ -4414,7 +4378,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>China Railway Construction Corporation</t>
+          <t>China Railway Construction Corporation (CRCC)</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -4437,12 +4401,22 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
+          <t>Carretera de Valencia a Toco y puerto de ferry de Toco</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
           <t>Valencia to Toco roadway and Toco ferry port</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
           <t>TUNAPUNA/PIARCO</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Construcción</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
@@ -4458,20 +4432,15 @@
       <c r="BA35" t="n">
         <v>2</v>
       </c>
-      <c r="BC35" t="n">
-        <v>1</v>
+      <c r="BB35" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC35" t="inlineStr">
+        <is>
+          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
+        </is>
       </c>
       <c r="BD35" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE35" t="inlineStr">
-        <is>
-          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
-        </is>
-      </c>
-      <c r="BF35" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
@@ -4501,7 +4470,7 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G36" s="1" t="inlineStr">
         <is>
           <t>780</t>
         </is>
@@ -4516,7 +4485,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>China Railway Construction Corporation</t>
+          <t>China Railway Construction Corporation (CRCC)</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -4539,12 +4508,22 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
+          <t>Carretera de Valencia a Toco y puerto de ferry de Toco</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
           <t>Valencia to Toco roadway and Toco ferry port</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
           <t>TUNAPUNA/PIARCO</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Construcción</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
@@ -4560,20 +4539,15 @@
       <c r="BA36" t="n">
         <v>2</v>
       </c>
-      <c r="BC36" t="n">
-        <v>1</v>
+      <c r="BB36" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC36" t="inlineStr">
+        <is>
+          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
+        </is>
       </c>
       <c r="BD36" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE36" t="inlineStr">
-        <is>
-          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
-        </is>
-      </c>
-      <c r="BF36" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
@@ -4590,7 +4564,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>10.79499172569179, -61.22448989378165</t>
+          <t>10.7890, -61.2245</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4603,7 +4577,7 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G37" s="1" t="inlineStr">
         <is>
           <t>780</t>
         </is>
@@ -4618,7 +4592,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>China Railway Construction Corporation</t>
+          <t>China Railway Construction Corporation (CRCC)</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -4641,12 +4615,22 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
+          <t>Carretera de Valencia a Toco y puerto de ferry de Toco</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
           <t>Valencia to Toco roadway and Toco ferry port</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>REVISAR - FUERA DE POLIGONOS</t>
+          <t>TUNAPUNA/PIARCO</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Construcción</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
@@ -4662,20 +4646,15 @@
       <c r="BA37" t="n">
         <v>2</v>
       </c>
-      <c r="BC37" t="n">
-        <v>1</v>
+      <c r="BB37" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC37" t="inlineStr">
+        <is>
+          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
+        </is>
       </c>
       <c r="BD37" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE37" t="inlineStr">
-        <is>
-          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
-        </is>
-      </c>
-      <c r="BF37" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
@@ -4692,7 +4671,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>10.79777113758367, -61.21980420456573</t>
+          <t>10.7900, -61.2198</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4705,7 +4684,7 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G38" s="1" t="inlineStr">
         <is>
           <t>780</t>
         </is>
@@ -4720,7 +4699,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>China Railway Construction Corporation</t>
+          <t>China Railway Construction Corporation (CRCC)</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -4743,12 +4722,22 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
+          <t>Carretera de Valencia a Toco y puerto de ferry de Toco</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
           <t>Valencia to Toco roadway and Toco ferry port</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>REVISAR - FUERA DE POLIGONOS</t>
+          <t>TUNAPUNA/PIARCO</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Construcción</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
@@ -4764,20 +4753,15 @@
       <c r="BA38" t="n">
         <v>2</v>
       </c>
-      <c r="BC38" t="n">
-        <v>1</v>
+      <c r="BB38" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC38" t="inlineStr">
+        <is>
+          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
+        </is>
       </c>
       <c r="BD38" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE38" t="inlineStr">
-        <is>
-          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
-        </is>
-      </c>
-      <c r="BF38" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
@@ -4807,7 +4791,7 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G39" s="1" t="inlineStr">
         <is>
           <t>780</t>
         </is>
@@ -4822,7 +4806,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>China Railway Construction Corporation</t>
+          <t>China Railway Construction Corporation (CRCC)</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -4845,12 +4829,22 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
+          <t>Carretera de Valencia a Toco y puerto de ferry de Toco</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
           <t>Valencia to Toco roadway and Toco ferry port</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
           <t>TUNAPUNA/PIARCO</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Construcción</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
@@ -4866,20 +4860,15 @@
       <c r="BA39" t="n">
         <v>2</v>
       </c>
-      <c r="BC39" t="n">
-        <v>1</v>
+      <c r="BB39" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC39" t="inlineStr">
+        <is>
+          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
+        </is>
       </c>
       <c r="BD39" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE39" t="inlineStr">
-        <is>
-          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
-        </is>
-      </c>
-      <c r="BF39" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
@@ -4909,7 +4898,7 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G40" s="1" t="inlineStr">
         <is>
           <t>780</t>
         </is>
@@ -4924,7 +4913,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>China Railway Construction Corporation</t>
+          <t>China Railway Construction Corporation (CRCC)</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -4947,12 +4936,22 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
+          <t>Carretera de Valencia a Toco y puerto de ferry de Toco</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
           <t>Valencia to Toco roadway and Toco ferry port</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
           <t>SANGRE GRANDE</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Construcción</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
@@ -4968,20 +4967,15 @@
       <c r="BA40" t="n">
         <v>2</v>
       </c>
-      <c r="BC40" t="n">
-        <v>1</v>
+      <c r="BB40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC40" t="inlineStr">
+        <is>
+          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
+        </is>
       </c>
       <c r="BD40" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE40" t="inlineStr">
-        <is>
-          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
-        </is>
-      </c>
-      <c r="BF40" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
@@ -5011,7 +5005,7 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G41" s="1" t="inlineStr">
         <is>
           <t>780</t>
         </is>
@@ -5026,7 +5020,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>China Railway Construction Corporation</t>
+          <t>China Railway Construction Corporation (CRCC)</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -5049,12 +5043,22 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
+          <t>Carretera de Valencia a Toco y puerto de ferry de Toco</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
           <t>Valencia to Toco roadway and Toco ferry port</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
           <t>SANGRE GRANDE</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Construcción</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
@@ -5070,20 +5074,15 @@
       <c r="BA41" t="n">
         <v>2</v>
       </c>
-      <c r="BC41" t="n">
-        <v>1</v>
+      <c r="BB41" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC41" t="inlineStr">
+        <is>
+          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
+        </is>
       </c>
       <c r="BD41" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE41" t="inlineStr">
-        <is>
-          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
-        </is>
-      </c>
-      <c r="BF41" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
@@ -5113,7 +5112,7 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G42" s="1" t="inlineStr">
         <is>
           <t>780</t>
         </is>
@@ -5128,7 +5127,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>China Railway Construction Corporation</t>
+          <t>China Railway Construction Corporation (CRCC)</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -5151,12 +5150,22 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
+          <t>Carretera de Valencia a Toco y puerto de ferry de Toco</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
           <t>Valencia to Toco roadway and Toco ferry port</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
           <t>SANGRE GRANDE</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Construcción</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
@@ -5172,20 +5181,15 @@
       <c r="BA42" t="n">
         <v>2</v>
       </c>
-      <c r="BC42" t="n">
-        <v>1</v>
+      <c r="BB42" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC42" t="inlineStr">
+        <is>
+          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
+        </is>
       </c>
       <c r="BD42" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE42" t="inlineStr">
-        <is>
-          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
-        </is>
-      </c>
-      <c r="BF42" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
@@ -5215,7 +5219,7 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G43" s="1" t="inlineStr">
         <is>
           <t>780</t>
         </is>
@@ -5230,7 +5234,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>China Railway Construction Corporation</t>
+          <t>China Railway Construction Corporation (CRCC)</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -5253,12 +5257,22 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
+          <t>Carretera de Valencia a Toco y puerto de ferry de Toco</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
           <t>Valencia to Toco roadway and Toco ferry port</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
           <t>SANGRE GRANDE</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Construcción</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
@@ -5274,20 +5288,15 @@
       <c r="BA43" t="n">
         <v>2</v>
       </c>
-      <c r="BC43" t="n">
-        <v>1</v>
+      <c r="BB43" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC43" t="inlineStr">
+        <is>
+          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
+        </is>
       </c>
       <c r="BD43" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE43" t="inlineStr">
-        <is>
-          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
-        </is>
-      </c>
-      <c r="BF43" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
@@ -5317,7 +5326,7 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G44" s="1" t="inlineStr">
         <is>
           <t>780</t>
         </is>
@@ -5332,7 +5341,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>China Railway Construction Corporation</t>
+          <t>China Railway Construction Corporation (CRCC)</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -5355,12 +5364,22 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
+          <t>Carretera de Valencia a Toco y puerto de ferry de Toco</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
           <t>Valencia to Toco roadway and Toco ferry port</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
           <t>SANGRE GRANDE</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Construcción</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
@@ -5376,20 +5395,15 @@
       <c r="BA44" t="n">
         <v>2</v>
       </c>
-      <c r="BC44" t="n">
-        <v>1</v>
+      <c r="BB44" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC44" t="inlineStr">
+        <is>
+          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
+        </is>
       </c>
       <c r="BD44" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE44" t="inlineStr">
-        <is>
-          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
-        </is>
-      </c>
-      <c r="BF44" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
@@ -5419,7 +5433,7 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G45" s="1" t="inlineStr">
         <is>
           <t>780</t>
         </is>
@@ -5434,7 +5448,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>China Railway Construction Corporation</t>
+          <t>China Railway Construction Corporation (CRCC)</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -5457,12 +5471,22 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
+          <t>Carretera de Valencia a Toco y puerto de ferry de Toco</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
           <t>Valencia to Toco roadway and Toco ferry port</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
           <t>SANGRE GRANDE</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Construcción</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
@@ -5478,20 +5502,15 @@
       <c r="BA45" t="n">
         <v>2</v>
       </c>
-      <c r="BC45" t="n">
-        <v>1</v>
+      <c r="BB45" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC45" t="inlineStr">
+        <is>
+          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
+        </is>
       </c>
       <c r="BD45" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE45" t="inlineStr">
-        <is>
-          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
-        </is>
-      </c>
-      <c r="BF45" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
@@ -5521,7 +5540,7 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G46" s="1" t="inlineStr">
         <is>
           <t>780</t>
         </is>
@@ -5536,7 +5555,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>China Railway Construction Corporation</t>
+          <t>China Railway Construction Corporation (CRCC)</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -5559,12 +5578,22 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
+          <t>Carretera de Valencia a Toco y puerto de ferry de Toco</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
           <t>Valencia to Toco roadway and Toco ferry port</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
           <t>SANGRE GRANDE</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Construcción</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
@@ -5580,20 +5609,15 @@
       <c r="BA46" t="n">
         <v>2</v>
       </c>
-      <c r="BC46" t="n">
-        <v>1</v>
+      <c r="BB46" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC46" t="inlineStr">
+        <is>
+          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
+        </is>
       </c>
       <c r="BD46" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE46" t="inlineStr">
-        <is>
-          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
-        </is>
-      </c>
-      <c r="BF46" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
@@ -5623,7 +5647,7 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G47" s="1" t="inlineStr">
         <is>
           <t>780</t>
         </is>
@@ -5638,7 +5662,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>China Railway Construction Corporation</t>
+          <t>China Railway Construction Corporation (CRCC)</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -5661,12 +5685,22 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
+          <t>Carretera de Valencia a Toco y puerto de ferry de Toco</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
           <t>Valencia to Toco roadway and Toco ferry port</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
           <t>SANGRE GRANDE</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Construcción</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
@@ -5682,20 +5716,15 @@
       <c r="BA47" t="n">
         <v>2</v>
       </c>
-      <c r="BC47" t="n">
-        <v>1</v>
+      <c r="BB47" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC47" t="inlineStr">
+        <is>
+          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
+        </is>
       </c>
       <c r="BD47" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE47" t="inlineStr">
-        <is>
-          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
-        </is>
-      </c>
-      <c r="BF47" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
@@ -5725,7 +5754,7 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G48" s="1" t="inlineStr">
         <is>
           <t>780</t>
         </is>
@@ -5740,7 +5769,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>China Railway Construction Corporation</t>
+          <t>China Railway Construction Corporation (CRCC)</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -5763,12 +5792,22 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
+          <t>Carretera de Valencia a Toco y puerto de ferry de Toco</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
           <t>Valencia to Toco roadway and Toco ferry port</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
           <t>SANGRE GRANDE</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Construcción</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
@@ -5784,20 +5823,15 @@
       <c r="BA48" t="n">
         <v>2</v>
       </c>
-      <c r="BC48" t="n">
-        <v>1</v>
+      <c r="BB48" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC48" t="inlineStr">
+        <is>
+          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
+        </is>
       </c>
       <c r="BD48" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE48" t="inlineStr">
-        <is>
-          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
-        </is>
-      </c>
-      <c r="BF48" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
@@ -5827,7 +5861,7 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G49" s="1" t="inlineStr">
         <is>
           <t>780</t>
         </is>
@@ -5842,7 +5876,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>China Railway Construction Corporation</t>
+          <t>China Railway Construction Corporation (CRCC)</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -5865,12 +5899,22 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
+          <t>Carretera de Valencia a Toco y puerto de ferry de Toco</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
           <t>Valencia to Toco roadway and Toco ferry port</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
           <t>SANGRE GRANDE</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Construcción</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
@@ -5886,20 +5930,15 @@
       <c r="BA49" t="n">
         <v>2</v>
       </c>
-      <c r="BC49" t="n">
-        <v>1</v>
+      <c r="BB49" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC49" t="inlineStr">
+        <is>
+          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
+        </is>
       </c>
       <c r="BD49" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE49" t="inlineStr">
-        <is>
-          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
-        </is>
-      </c>
-      <c r="BF49" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
@@ -5929,7 +5968,7 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G50" s="1" t="inlineStr">
         <is>
           <t>780</t>
         </is>
@@ -5944,7 +5983,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>China Railway Construction Corporation</t>
+          <t>China Railway Construction Corporation (CRCC)</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -5967,12 +6006,22 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
+          <t>Carretera de Valencia a Toco y puerto de ferry de Toco</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
           <t>Valencia to Toco roadway and Toco ferry port</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
           <t>SANGRE GRANDE</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Construcción</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
@@ -5988,20 +6037,15 @@
       <c r="BA50" t="n">
         <v>2</v>
       </c>
-      <c r="BC50" t="n">
-        <v>1</v>
+      <c r="BB50" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC50" t="inlineStr">
+        <is>
+          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
+        </is>
       </c>
       <c r="BD50" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE50" t="inlineStr">
-        <is>
-          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
-        </is>
-      </c>
-      <c r="BF50" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
@@ -6031,7 +6075,7 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G51" s="1" t="inlineStr">
         <is>
           <t>780</t>
         </is>
@@ -6046,7 +6090,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>China Railway Construction Corporation</t>
+          <t>China Railway Construction Corporation (CRCC)</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -6068,6 +6112,11 @@
         </is>
       </c>
       <c r="O51" t="inlineStr">
+        <is>
+          <t>Carretera de Valencia a Toco y puerto de ferry de Toco</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
         <is>
           <t>Valencia to Toco roadway and Toco ferry port</t>
         </is>
@@ -6095,20 +6144,15 @@
       <c r="BA51" t="n">
         <v>2</v>
       </c>
-      <c r="BC51" t="n">
-        <v>1</v>
+      <c r="BB51" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC51" t="inlineStr">
+        <is>
+          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
+        </is>
       </c>
       <c r="BD51" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE51" t="inlineStr">
-        <is>
-          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
-        </is>
-      </c>
-      <c r="BF51" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
@@ -6138,7 +6182,7 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G52" s="1" t="inlineStr">
         <is>
           <t>780</t>
         </is>
@@ -6176,7 +6220,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Valencia to Toco roadway and Toco ferry port</t>
+          <t>Academia de Críquet Brian Lara en Tarouba</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6207,25 +6251,20 @@
       <c r="BA52" t="n">
         <v>2</v>
       </c>
-      <c r="BC52" t="n">
-        <v>1</v>
+      <c r="BB52" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC52" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Brian_Lara_Cricket_Academy</t>
+        </is>
       </c>
       <c r="BD52" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
         </is>
       </c>
       <c r="BE52" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Brian_Lara_Cricket_Academy</t>
-        </is>
-      </c>
-      <c r="BF52" t="inlineStr">
-        <is>
-          <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
-        </is>
-      </c>
-      <c r="BG52" t="inlineStr">
         <is>
           <t>https://udecott.com/projects/brian-lara-cricket-academy/</t>
         </is>

--- a/data/sources/countries/trinidad_and_tobago.xlsx
+++ b/data/sources/countries/trinidad_and_tobago.xlsx
@@ -46,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE52"/>
+  <dimension ref="A1:BG52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -685,20 +684,30 @@
       </c>
       <c r="BB1" t="inlineStr">
         <is>
+          <t>reliability_notes</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
           <t>cancelled</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>cancelled_motivo</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
         <is>
           <t>source1</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>source2</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>source3</t>
         </is>
@@ -710,6 +719,7 @@
           <t>TTO-0001</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
         <v>1</v>
       </c>
@@ -728,11 +738,10 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
-      </c>
+      <c r="G2" t="n">
+        <v>780</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
         <v>2009</v>
       </c>
@@ -777,6 +786,7 @@
       <c r="R2" t="n">
         <v>250</v>
       </c>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr">
         <is>
           <t>Talisman Energy (Canada)</t>
@@ -800,23 +810,53 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="n">
         <v>3</v>
       </c>
-      <c r="BB2" t="n">
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="n">
         <v>0</v>
       </c>
-      <c r="BC2" t="inlineStr">
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/0001095595/000095010309001714/dp14160_6k.htm</t>
         </is>
       </c>
-      <c r="BD2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/0001095595/000095010310001157/dp17202_ex1502.htm</t>
         </is>
       </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>https://www.guardian.co.tt/article-6.2.450605.98b132e9ca</t>
         </is>
@@ -828,6 +868,7 @@
           <t>TTO-0002</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>2</v>
       </c>
@@ -846,10 +887,8 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
+      <c r="G3" t="n">
+        <v>780</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -900,6 +939,9 @@
       <c r="R3" t="n">
         <v>120</v>
       </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -915,23 +957,53 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="n">
         <v>3</v>
       </c>
-      <c r="BB3" t="n">
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="n">
         <v>0</v>
       </c>
-      <c r="BC3" t="inlineStr">
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr">
         <is>
           <t>https://www.guardian.co.tt/article-6.2.408731.3817c8f714</t>
         </is>
       </c>
-      <c r="BD3" t="inlineStr">
+      <c r="BF3" t="inlineStr">
         <is>
           <t>https://www.globalconstructionreview.com/chinese-firms-fund-and-build-160m-hospital-trinida</t>
         </is>
       </c>
-      <c r="BE3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>https://newsday.co.tt/2019/03/07/china-railways-road-in-tt/</t>
         </is>
@@ -943,6 +1015,7 @@
           <t>TTO-0003</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
         <v>3</v>
       </c>
@@ -961,10 +1034,8 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G4" s="1" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
+      <c r="G4" t="n">
+        <v>780</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1012,6 +1083,10 @@
           <t>TUNAPUNA/PIARCO</t>
         </is>
       </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1027,23 +1102,53 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="n">
         <v>3</v>
       </c>
-      <c r="BB4" t="n">
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="n">
         <v>0</v>
       </c>
-      <c r="BC4" t="inlineStr">
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr">
         <is>
           <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
         </is>
       </c>
-      <c r="BD4" t="inlineStr">
+      <c r="BF4" t="inlineStr">
         <is>
           <t>https://trinidadexpress.com/news/local/from-shanghai-to-trinidad/article_d4507526-0182-55f7-89d1-cfde43c8bf74.html</t>
         </is>
       </c>
-      <c r="BE4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>https://globalamericans.org/chinas-engagement-with-trinidad-and-tobago/</t>
         </is>
@@ -1055,6 +1160,7 @@
           <t>TTO-0004</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
         <v>4</v>
       </c>
@@ -1073,10 +1179,8 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G5" s="1" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
+      <c r="G5" t="n">
+        <v>780</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1127,6 +1231,9 @@
       <c r="R5" t="n">
         <v>71</v>
       </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1142,23 +1249,53 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
         <v>3</v>
       </c>
-      <c r="BB5" t="n">
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="n">
         <v>0</v>
       </c>
-      <c r="BC5" t="inlineStr">
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr">
         <is>
           <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
         </is>
       </c>
-      <c r="BD5" t="inlineStr">
+      <c r="BF5" t="inlineStr">
         <is>
           <t>https://universalprojectsltd.com/wordpress/aquatic-center/</t>
         </is>
       </c>
-      <c r="BE5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>https://sportt-tt.com/book-a-facility/national-aquatic-centre/</t>
         </is>
@@ -1170,6 +1307,7 @@
           <t>TTO-0005</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
         <v>5</v>
       </c>
@@ -1188,10 +1326,8 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G6" s="1" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
+      <c r="G6" t="n">
+        <v>780</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1242,6 +1378,9 @@
       <c r="R6" t="n">
         <v>97</v>
       </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1257,23 +1396,53 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="n">
         <v>4</v>
       </c>
-      <c r="BB6" t="n">
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="n">
         <v>0</v>
       </c>
-      <c r="BC6" t="inlineStr">
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr">
         <is>
           <t>https://en.powerchina.cn/2019-07/19/c_714119.htm</t>
         </is>
       </c>
-      <c r="BD6" t="inlineStr">
+      <c r="BF6" t="inlineStr">
         <is>
           <t>https://archives.newsday.co.tt/2015/04/30/chinese-to-build-620m-wastewater-plant/</t>
         </is>
       </c>
-      <c r="BE6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>https://archives.newsday.co.tt/2014/11/18/us579-million-to-build-wastewater-plants/</t>
         </is>
@@ -1285,6 +1454,7 @@
           <t>TTO-0006</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
         <v>6</v>
       </c>
@@ -1303,10 +1473,8 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G7" s="1" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
+      <c r="G7" t="n">
+        <v>780</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1357,6 +1525,9 @@
       <c r="R7" t="n">
         <v>104</v>
       </c>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1372,23 +1543,53 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="n">
         <v>4</v>
       </c>
-      <c r="BB7" t="n">
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="n">
         <v>0</v>
       </c>
-      <c r="BC7" t="inlineStr">
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr">
         <is>
           <t>https://trinidadexpress.com/business/local/china-to-fund-phoenix-park-industrial-estate/article_31be9880-7498-11e8-aa35-134f694d9978.html</t>
         </is>
       </c>
-      <c r="BD7" t="inlineStr">
+      <c r="BF7" t="inlineStr">
         <is>
           <t>https://eteck.co.tt/index.php/2018/06/21/684/</t>
         </is>
       </c>
-      <c r="BE7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>https://tradeind.gov.tt/chinese_firms_invest_phoenix_industrial_estate/</t>
         </is>
@@ -1400,6 +1601,7 @@
           <t>TTO-0007</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
         <v>7</v>
       </c>
@@ -1418,10 +1620,8 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G8" s="1" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
+      <c r="G8" t="n">
+        <v>780</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1472,6 +1672,9 @@
       <c r="R8" t="n">
         <v>160</v>
       </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1487,22 +1690,53 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="n">
         <v>4</v>
       </c>
-      <c r="BB8" t="n">
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="n">
         <v>0</v>
       </c>
-      <c r="BC8" t="inlineStr">
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr">
         <is>
           <t>https://www.globalconstructionreview.com/chinese-firms-fund-and-build-160m-hospital-trinida</t>
         </is>
       </c>
-      <c r="BD8" t="inlineStr">
+      <c r="BF8" t="inlineStr">
         <is>
           <t>https://www.globenewswire.com/news-release/2024/07/17/2914346/0/en/CRCC-Spearheading-the-Modernization-of-Port-of-Spain-General-Hospital.html</t>
         </is>
       </c>
+      <c r="BG8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1510,6 +1744,7 @@
           <t>TTO-0008</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
         <v>8</v>
       </c>
@@ -1528,10 +1763,8 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G9" s="1" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
+      <c r="G9" t="n">
+        <v>780</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1579,6 +1812,10 @@
           <t>COUVA-TABAQUITE-TALPARO</t>
         </is>
       </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
           <t>Greenfield</t>
@@ -1594,23 +1831,53 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
       <c r="BA9" t="n">
         <v>4</v>
       </c>
-      <c r="BB9" t="n">
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="n">
         <v>0</v>
       </c>
-      <c r="BC9" t="inlineStr">
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr">
         <is>
           <t>https://businessfacilities.com/two-china-based-companies-choose-trinidad-and-tobago-location</t>
         </is>
       </c>
-      <c r="BD9" t="inlineStr">
+      <c r="BF9" t="inlineStr">
         <is>
           <t>https://tradeind.gov.tt/chinese_firms_invest_phoenix_industrial_estate/</t>
         </is>
       </c>
-      <c r="BE9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>http://www.china.org.cn/world/Off_the_Wire/2023-09/23/content_116705829.htm</t>
         </is>
@@ -1622,6 +1889,7 @@
           <t>TTO-0009</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
         <v>9</v>
       </c>
@@ -1640,11 +1908,10 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G10" s="1" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
-      </c>
+      <c r="G10" t="n">
+        <v>780</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
         <v>2026</v>
       </c>
@@ -1686,6 +1953,10 @@
           <t>REVISAR - FUERA DE POLIGONOS</t>
         </is>
       </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
           <t>Adquisición</t>
@@ -1701,23 +1972,53 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
       <c r="BA10" t="n">
         <v>4</v>
       </c>
-      <c r="BB10" t="n">
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="n">
         <v>0</v>
       </c>
-      <c r="BC10" t="inlineStr">
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr">
         <is>
           <t>https://www.guardian.co.tt/business/tt-awards-two-offshore-blocks-to-chinese-state-company-6.2.2531632.001835bac9</t>
         </is>
       </c>
-      <c r="BD10" t="inlineStr">
+      <c r="BF10" t="inlineStr">
         <is>
           <t>https://oilnow.gy/news/chinese-oil-giant-leads-interest-in-trinidad-deepwater-blocks/</t>
         </is>
       </c>
-      <c r="BE10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>https://www.energy.gov.tt/trinidad-and-tobago-welcomes-new-entrants-to-its-deep-water-frontier/</t>
         </is>
@@ -1729,6 +2030,7 @@
           <t>TTO-0010</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
         <v>10</v>
       </c>
@@ -1747,10 +2049,8 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G11" s="1" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
+      <c r="G11" t="n">
+        <v>780</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1801,6 +2101,9 @@
       <c r="R11" t="n">
         <v>33</v>
       </c>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1816,23 +2119,53 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr"/>
       <c r="BA11" t="n">
         <v>5</v>
       </c>
-      <c r="BB11" t="n">
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="n">
         <v>0</v>
       </c>
-      <c r="BC11" t="inlineStr">
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr">
         <is>
           <t>https://mowt.gov.tt/Divisions/Highways-Division/Projects/The-Curepe-Interchange-Project</t>
         </is>
       </c>
-      <c r="BD11" t="inlineStr">
+      <c r="BF11" t="inlineStr">
         <is>
           <t>https://newsday.co.tt/2019/03/07/china-railways-road-in-tt/</t>
         </is>
       </c>
-      <c r="BE11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>https://eng.yidaiyilu.gov.cn/p/290666.html</t>
         </is>
@@ -1844,6 +2177,7 @@
           <t>TTO-0011</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
         <v>11</v>
       </c>
@@ -1862,10 +2196,8 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G12" s="1" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
+      <c r="G12" t="n">
+        <v>780</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1916,6 +2248,9 @@
       <c r="R12" t="n">
         <v>144</v>
       </c>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1931,23 +2266,53 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr"/>
       <c r="BA12" t="n">
         <v>5</v>
       </c>
-      <c r="BB12" t="n">
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="n">
         <v>0</v>
       </c>
-      <c r="BC12" t="inlineStr">
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr">
         <is>
           <t>https://www.airport-technology.com/projects/anr-robinson-international-airport-expansion-project/</t>
         </is>
       </c>
-      <c r="BD12" t="inlineStr">
+      <c r="BF12" t="inlineStr">
         <is>
           <t>https://newsday.co.tt/2025/08/16/no-date-set-for-opening-of-anr-robinson-airport/</t>
         </is>
       </c>
-      <c r="BE12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>https://trinidadexpress.com/newsextra/chinese-company-to-resume-construction-of-airport-terminal-in-tobago/article_41438dcc-dc2a-11eb-8c53-df98c00fb914.html</t>
         </is>
@@ -1959,6 +2324,7 @@
           <t>TTO-0012</t>
         </is>
       </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
         <v>12</v>
       </c>
@@ -1977,10 +2343,8 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G13" s="1" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
+      <c r="G13" t="n">
+        <v>780</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -2031,6 +2395,7 @@
       <c r="R13" t="n">
         <v>850</v>
       </c>
+      <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr">
         <is>
           <t>GDF Suez (Francia)</t>
@@ -2054,23 +2419,53 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr"/>
       <c r="BA13" t="n">
         <v>4</v>
       </c>
-      <c r="BB13" t="n">
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="n">
         <v>1</v>
       </c>
-      <c r="BC13" t="inlineStr">
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr">
         <is>
           <t>https://www.hartenergy.com/news/chinese-firm-takes-over-share-atlantic-lng-91768</t>
         </is>
       </c>
-      <c r="BD13" t="inlineStr">
+      <c r="BF13" t="inlineStr">
         <is>
           <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
         </is>
       </c>
-      <c r="BE13" t="inlineStr">
+      <c r="BG13" t="inlineStr">
         <is>
           <t>https://www.guardian.co.tt/article-6.2.448448.b331a5af49</t>
         </is>
@@ -2082,6 +2477,7 @@
           <t>TTO-0013</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
         <v>13</v>
       </c>
@@ -2100,10 +2496,8 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G14" s="1" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
+      <c r="G14" t="n">
+        <v>780</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -2154,6 +2548,9 @@
       <c r="R14" t="n">
         <v>150</v>
       </c>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2169,23 +2566,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr"/>
+      <c r="AX14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr"/>
       <c r="BA14" t="n">
         <v>4</v>
       </c>
-      <c r="BB14" t="n">
+      <c r="BB14" t="inlineStr"/>
+      <c r="BC14" t="n">
         <v>1</v>
       </c>
-      <c r="BC14" t="inlineStr">
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
         <is>
           <t>https://udecott.com/projects/the-couva-childrens-hospital-and-multi-training-facility/</t>
         </is>
       </c>
-      <c r="BD14" t="inlineStr">
+      <c r="BF14" t="inlineStr">
         <is>
           <t>https://www.cnc3.co.tt/hospital-on-hold/</t>
         </is>
       </c>
-      <c r="BE14" t="inlineStr">
+      <c r="BG14" t="inlineStr">
         <is>
           <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
         </is>
@@ -2197,6 +2628,7 @@
           <t>TTO-0014</t>
         </is>
       </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
         <v>14</v>
       </c>
@@ -2215,10 +2647,8 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G15" s="1" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
+      <c r="G15" t="n">
+        <v>780</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -2269,6 +2699,9 @@
       <c r="R15" t="n">
         <v>590</v>
       </c>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
           <t>Adquisición</t>
@@ -2284,23 +2717,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr"/>
+      <c r="AX15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr"/>
       <c r="BA15" t="n">
         <v>1</v>
       </c>
-      <c r="BB15" t="n">
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="n">
         <v>1</v>
       </c>
-      <c r="BC15" t="inlineStr">
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
         <is>
           <t>https://newsday.co.tt/2021/12/20/a-dry-dock-comes-to-la-brea/</t>
         </is>
       </c>
-      <c r="BD15" t="inlineStr">
+      <c r="BF15" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/La-Brea-Dry-Docking-Facility</t>
         </is>
       </c>
-      <c r="BE15" t="inlineStr">
+      <c r="BG15" t="inlineStr">
         <is>
           <t>https://www.cijn.org/chinas-opaque-caribbean-trail-dreams-deals-and-debt/</t>
         </is>
@@ -2312,6 +2779,7 @@
           <t>TTO-0015</t>
         </is>
       </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
         <v>15</v>
       </c>
@@ -2330,10 +2798,8 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G16" s="1" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
+      <c r="G16" t="n">
+        <v>780</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -2381,6 +2847,10 @@
           <t>TUNAPUNA/PIARCO</t>
         </is>
       </c>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr">
         <is>
           <t>Greenfield</t>
@@ -2396,22 +2866,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AU16" t="inlineStr"/>
+      <c r="AV16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr"/>
+      <c r="AX16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr"/>
       <c r="BA16" t="n">
         <v>2</v>
       </c>
-      <c r="BB16" t="n">
+      <c r="BB16" t="inlineStr"/>
+      <c r="BC16" t="n">
         <v>1</v>
       </c>
-      <c r="BC16" t="inlineStr">
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
         <is>
           <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
         </is>
       </c>
-      <c r="BD16" t="inlineStr">
+      <c r="BF16" t="inlineStr">
         <is>
           <t>https://econvue.com/pulse/china%E2%80%99s-engagement-trinidad-and-tobago</t>
         </is>
       </c>
+      <c r="BG16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2419,6 +2924,7 @@
           <t>TTO-0016</t>
         </is>
       </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
         <v>16</v>
       </c>
@@ -2437,10 +2943,8 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G17" s="1" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
+      <c r="G17" t="n">
+        <v>780</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -2488,6 +2992,10 @@
           <t>SAN JUAN-LAVENTILLE</t>
         </is>
       </c>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2503,22 +3011,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr"/>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AU17" t="inlineStr"/>
+      <c r="AV17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr"/>
+      <c r="AX17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr"/>
       <c r="BA17" t="n">
         <v>2</v>
       </c>
-      <c r="BB17" t="n">
+      <c r="BB17" t="inlineStr"/>
+      <c r="BC17" t="n">
         <v>1</v>
       </c>
-      <c r="BC17" t="inlineStr">
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
         <is>
           <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
         </is>
       </c>
-      <c r="BD17" t="inlineStr">
+      <c r="BF17" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
       </c>
+      <c r="BG17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2526,6 +3069,7 @@
           <t>TTO-0016</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
         <v>16</v>
       </c>
@@ -2544,10 +3088,8 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G18" s="1" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
+      <c r="G18" t="n">
+        <v>780</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2595,6 +3137,10 @@
           <t>SAN JUAN-LAVENTILLE</t>
         </is>
       </c>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2610,22 +3156,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="inlineStr"/>
+      <c r="AQ18" t="inlineStr"/>
+      <c r="AR18" t="inlineStr"/>
+      <c r="AS18" t="inlineStr"/>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AU18" t="inlineStr"/>
+      <c r="AV18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr"/>
+      <c r="AX18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr"/>
       <c r="BA18" t="n">
         <v>2</v>
       </c>
-      <c r="BB18" t="n">
+      <c r="BB18" t="inlineStr"/>
+      <c r="BC18" t="n">
         <v>1</v>
       </c>
-      <c r="BC18" t="inlineStr">
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
         <is>
           <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
         </is>
       </c>
-      <c r="BD18" t="inlineStr">
+      <c r="BF18" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
       </c>
+      <c r="BG18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2633,6 +3214,7 @@
           <t>TTO-0016</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
         <v>16</v>
       </c>
@@ -2651,10 +3233,8 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G19" s="1" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
+      <c r="G19" t="n">
+        <v>780</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2702,6 +3282,10 @@
           <t>SAN JUAN-LAVENTILLE</t>
         </is>
       </c>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2717,22 +3301,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr"/>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="inlineStr"/>
+      <c r="AP19" t="inlineStr"/>
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="inlineStr"/>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AU19" t="inlineStr"/>
+      <c r="AV19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr"/>
+      <c r="AX19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr"/>
       <c r="BA19" t="n">
         <v>2</v>
       </c>
-      <c r="BB19" t="n">
+      <c r="BB19" t="inlineStr"/>
+      <c r="BC19" t="n">
         <v>1</v>
       </c>
-      <c r="BC19" t="inlineStr">
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
         <is>
           <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
         </is>
       </c>
-      <c r="BD19" t="inlineStr">
+      <c r="BF19" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
       </c>
+      <c r="BG19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2740,6 +3359,7 @@
           <t>TTO-0016</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
         <v>16</v>
       </c>
@@ -2758,10 +3378,8 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G20" s="1" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
+      <c r="G20" t="n">
+        <v>780</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2809,6 +3427,10 @@
           <t>SAN JUAN-LAVENTILLE</t>
         </is>
       </c>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2824,22 +3446,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="inlineStr"/>
+      <c r="AP20" t="inlineStr"/>
+      <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AU20" t="inlineStr"/>
+      <c r="AV20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr"/>
+      <c r="AX20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr"/>
       <c r="BA20" t="n">
         <v>2</v>
       </c>
-      <c r="BB20" t="n">
+      <c r="BB20" t="inlineStr"/>
+      <c r="BC20" t="n">
         <v>1</v>
       </c>
-      <c r="BC20" t="inlineStr">
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE20" t="inlineStr">
         <is>
           <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
         </is>
       </c>
-      <c r="BD20" t="inlineStr">
+      <c r="BF20" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
       </c>
+      <c r="BG20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2847,6 +3504,7 @@
           <t>TTO-0016</t>
         </is>
       </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
         <v>16</v>
       </c>
@@ -2865,10 +3523,8 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G21" s="1" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
+      <c r="G21" t="n">
+        <v>780</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2916,6 +3572,10 @@
           <t>SAN JUAN-LAVENTILLE</t>
         </is>
       </c>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2931,22 +3591,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr"/>
+      <c r="AO21" t="inlineStr"/>
+      <c r="AP21" t="inlineStr"/>
+      <c r="AQ21" t="inlineStr"/>
+      <c r="AR21" t="inlineStr"/>
+      <c r="AS21" t="inlineStr"/>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AU21" t="inlineStr"/>
+      <c r="AV21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr"/>
+      <c r="AX21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr"/>
       <c r="BA21" t="n">
         <v>2</v>
       </c>
-      <c r="BB21" t="n">
+      <c r="BB21" t="inlineStr"/>
+      <c r="BC21" t="n">
         <v>1</v>
       </c>
-      <c r="BC21" t="inlineStr">
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE21" t="inlineStr">
         <is>
           <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
         </is>
       </c>
-      <c r="BD21" t="inlineStr">
+      <c r="BF21" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
       </c>
+      <c r="BG21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2954,6 +3649,7 @@
           <t>TTO-0016</t>
         </is>
       </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
         <v>16</v>
       </c>
@@ -2972,10 +3668,8 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G22" s="1" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
+      <c r="G22" t="n">
+        <v>780</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -3023,6 +3717,10 @@
           <t>TUNAPUNA/PIARCO</t>
         </is>
       </c>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3038,22 +3736,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="inlineStr"/>
+      <c r="AP22" t="inlineStr"/>
+      <c r="AQ22" t="inlineStr"/>
+      <c r="AR22" t="inlineStr"/>
+      <c r="AS22" t="inlineStr"/>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AU22" t="inlineStr"/>
+      <c r="AV22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr"/>
+      <c r="AX22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr"/>
       <c r="BA22" t="n">
         <v>2</v>
       </c>
-      <c r="BB22" t="n">
+      <c r="BB22" t="inlineStr"/>
+      <c r="BC22" t="n">
         <v>1</v>
       </c>
-      <c r="BC22" t="inlineStr">
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE22" t="inlineStr">
         <is>
           <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
         </is>
       </c>
-      <c r="BD22" t="inlineStr">
+      <c r="BF22" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
       </c>
+      <c r="BG22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3061,6 +3794,7 @@
           <t>TTO-0016</t>
         </is>
       </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
         <v>16</v>
       </c>
@@ -3079,10 +3813,8 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G23" s="1" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
+      <c r="G23" t="n">
+        <v>780</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -3130,6 +3862,10 @@
           <t>TUNAPUNA/PIARCO</t>
         </is>
       </c>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3145,22 +3881,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="inlineStr"/>
+      <c r="AP23" t="inlineStr"/>
+      <c r="AQ23" t="inlineStr"/>
+      <c r="AR23" t="inlineStr"/>
+      <c r="AS23" t="inlineStr"/>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AU23" t="inlineStr"/>
+      <c r="AV23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr"/>
+      <c r="AX23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr"/>
       <c r="BA23" t="n">
         <v>2</v>
       </c>
-      <c r="BB23" t="n">
+      <c r="BB23" t="inlineStr"/>
+      <c r="BC23" t="n">
         <v>1</v>
       </c>
-      <c r="BC23" t="inlineStr">
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE23" t="inlineStr">
         <is>
           <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
         </is>
       </c>
-      <c r="BD23" t="inlineStr">
+      <c r="BF23" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
       </c>
+      <c r="BG23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3168,6 +3939,7 @@
           <t>TTO-0016</t>
         </is>
       </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>16</v>
       </c>
@@ -3186,10 +3958,8 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G24" s="1" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
+      <c r="G24" t="n">
+        <v>780</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -3237,6 +4007,10 @@
           <t>TUNAPUNA/PIARCO</t>
         </is>
       </c>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3252,22 +4026,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
+      <c r="AP24" t="inlineStr"/>
+      <c r="AQ24" t="inlineStr"/>
+      <c r="AR24" t="inlineStr"/>
+      <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AU24" t="inlineStr"/>
+      <c r="AV24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr"/>
+      <c r="AX24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr"/>
       <c r="BA24" t="n">
         <v>2</v>
       </c>
-      <c r="BB24" t="n">
+      <c r="BB24" t="inlineStr"/>
+      <c r="BC24" t="n">
         <v>1</v>
       </c>
-      <c r="BC24" t="inlineStr">
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE24" t="inlineStr">
         <is>
           <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
         </is>
       </c>
-      <c r="BD24" t="inlineStr">
+      <c r="BF24" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
       </c>
+      <c r="BG24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3275,6 +4084,7 @@
           <t>TTO-0016</t>
         </is>
       </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
         <v>16</v>
       </c>
@@ -3293,10 +4103,8 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G25" s="1" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
+      <c r="G25" t="n">
+        <v>780</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -3344,6 +4152,10 @@
           <t>TUNAPUNA/PIARCO</t>
         </is>
       </c>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3359,22 +4171,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
+      <c r="AP25" t="inlineStr"/>
+      <c r="AQ25" t="inlineStr"/>
+      <c r="AR25" t="inlineStr"/>
+      <c r="AS25" t="inlineStr"/>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AU25" t="inlineStr"/>
+      <c r="AV25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr"/>
+      <c r="AX25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr"/>
       <c r="BA25" t="n">
         <v>2</v>
       </c>
-      <c r="BB25" t="n">
+      <c r="BB25" t="inlineStr"/>
+      <c r="BC25" t="n">
         <v>1</v>
       </c>
-      <c r="BC25" t="inlineStr">
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE25" t="inlineStr">
         <is>
           <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
         </is>
       </c>
-      <c r="BD25" t="inlineStr">
+      <c r="BF25" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
       </c>
+      <c r="BG25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3382,6 +4229,7 @@
           <t>TTO-0016</t>
         </is>
       </c>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
         <v>16</v>
       </c>
@@ -3400,10 +4248,8 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G26" s="1" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
+      <c r="G26" t="n">
+        <v>780</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -3451,6 +4297,10 @@
           <t>SAN JUAN-LAVENTILLE</t>
         </is>
       </c>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3466,22 +4316,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr"/>
+      <c r="AJ26" t="inlineStr"/>
+      <c r="AK26" t="inlineStr"/>
+      <c r="AL26" t="inlineStr"/>
+      <c r="AM26" t="inlineStr"/>
+      <c r="AN26" t="inlineStr"/>
+      <c r="AO26" t="inlineStr"/>
+      <c r="AP26" t="inlineStr"/>
+      <c r="AQ26" t="inlineStr"/>
+      <c r="AR26" t="inlineStr"/>
+      <c r="AS26" t="inlineStr"/>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AU26" t="inlineStr"/>
+      <c r="AV26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr"/>
+      <c r="AX26" t="inlineStr"/>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr"/>
       <c r="BA26" t="n">
         <v>2</v>
       </c>
-      <c r="BB26" t="n">
+      <c r="BB26" t="inlineStr"/>
+      <c r="BC26" t="n">
         <v>1</v>
       </c>
-      <c r="BC26" t="inlineStr">
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE26" t="inlineStr">
         <is>
           <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
         </is>
       </c>
-      <c r="BD26" t="inlineStr">
+      <c r="BF26" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
       </c>
+      <c r="BG26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3489,6 +4374,7 @@
           <t>TTO-0016</t>
         </is>
       </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
         <v>16</v>
       </c>
@@ -3507,10 +4393,8 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G27" s="1" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
+      <c r="G27" t="n">
+        <v>780</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -3558,6 +4442,10 @@
           <t>TUNAPUNA/PIARCO</t>
         </is>
       </c>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3573,22 +4461,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="inlineStr"/>
+      <c r="AK27" t="inlineStr"/>
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="inlineStr"/>
+      <c r="AN27" t="inlineStr"/>
+      <c r="AO27" t="inlineStr"/>
+      <c r="AP27" t="inlineStr"/>
+      <c r="AQ27" t="inlineStr"/>
+      <c r="AR27" t="inlineStr"/>
+      <c r="AS27" t="inlineStr"/>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AU27" t="inlineStr"/>
+      <c r="AV27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr"/>
+      <c r="AX27" t="inlineStr"/>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr"/>
       <c r="BA27" t="n">
         <v>2</v>
       </c>
-      <c r="BB27" t="n">
+      <c r="BB27" t="inlineStr"/>
+      <c r="BC27" t="n">
         <v>1</v>
       </c>
-      <c r="BC27" t="inlineStr">
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE27" t="inlineStr">
         <is>
           <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
         </is>
       </c>
-      <c r="BD27" t="inlineStr">
+      <c r="BF27" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
       </c>
+      <c r="BG27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3596,6 +4519,7 @@
           <t>TTO-0016</t>
         </is>
       </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
         <v>16</v>
       </c>
@@ -3614,10 +4538,8 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G28" s="1" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
+      <c r="G28" t="n">
+        <v>780</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -3665,6 +4587,10 @@
           <t>TUNAPUNA/PIARCO</t>
         </is>
       </c>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3680,22 +4606,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr"/>
+      <c r="AJ28" t="inlineStr"/>
+      <c r="AK28" t="inlineStr"/>
+      <c r="AL28" t="inlineStr"/>
+      <c r="AM28" t="inlineStr"/>
+      <c r="AN28" t="inlineStr"/>
+      <c r="AO28" t="inlineStr"/>
+      <c r="AP28" t="inlineStr"/>
+      <c r="AQ28" t="inlineStr"/>
+      <c r="AR28" t="inlineStr"/>
+      <c r="AS28" t="inlineStr"/>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AU28" t="inlineStr"/>
+      <c r="AV28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr"/>
+      <c r="AX28" t="inlineStr"/>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr"/>
       <c r="BA28" t="n">
         <v>2</v>
       </c>
-      <c r="BB28" t="n">
+      <c r="BB28" t="inlineStr"/>
+      <c r="BC28" t="n">
         <v>1</v>
       </c>
-      <c r="BC28" t="inlineStr">
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE28" t="inlineStr">
         <is>
           <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
         </is>
       </c>
-      <c r="BD28" t="inlineStr">
+      <c r="BF28" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
       </c>
+      <c r="BG28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3703,6 +4664,7 @@
           <t>TTO-0016</t>
         </is>
       </c>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
         <v>16</v>
       </c>
@@ -3721,10 +4683,8 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G29" s="1" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
+      <c r="G29" t="n">
+        <v>780</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -3772,6 +4732,10 @@
           <t>TUNAPUNA/PIARCO</t>
         </is>
       </c>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3787,22 +4751,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr"/>
+      <c r="AJ29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr"/>
+      <c r="AL29" t="inlineStr"/>
+      <c r="AM29" t="inlineStr"/>
+      <c r="AN29" t="inlineStr"/>
+      <c r="AO29" t="inlineStr"/>
+      <c r="AP29" t="inlineStr"/>
+      <c r="AQ29" t="inlineStr"/>
+      <c r="AR29" t="inlineStr"/>
+      <c r="AS29" t="inlineStr"/>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AU29" t="inlineStr"/>
+      <c r="AV29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr"/>
+      <c r="AX29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr"/>
       <c r="BA29" t="n">
         <v>2</v>
       </c>
-      <c r="BB29" t="n">
+      <c r="BB29" t="inlineStr"/>
+      <c r="BC29" t="n">
         <v>1</v>
       </c>
-      <c r="BC29" t="inlineStr">
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE29" t="inlineStr">
         <is>
           <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
         </is>
       </c>
-      <c r="BD29" t="inlineStr">
+      <c r="BF29" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
       </c>
+      <c r="BG29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3810,6 +4809,7 @@
           <t>TTO-0016</t>
         </is>
       </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
         <v>16</v>
       </c>
@@ -3828,10 +4828,8 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G30" s="1" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
+      <c r="G30" t="n">
+        <v>780</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -3879,6 +4877,10 @@
           <t>TUNAPUNA/PIARCO</t>
         </is>
       </c>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3894,22 +4896,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr"/>
+      <c r="AJ30" t="inlineStr"/>
+      <c r="AK30" t="inlineStr"/>
+      <c r="AL30" t="inlineStr"/>
+      <c r="AM30" t="inlineStr"/>
+      <c r="AN30" t="inlineStr"/>
+      <c r="AO30" t="inlineStr"/>
+      <c r="AP30" t="inlineStr"/>
+      <c r="AQ30" t="inlineStr"/>
+      <c r="AR30" t="inlineStr"/>
+      <c r="AS30" t="inlineStr"/>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AU30" t="inlineStr"/>
+      <c r="AV30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr"/>
+      <c r="AX30" t="inlineStr"/>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr"/>
       <c r="BA30" t="n">
         <v>2</v>
       </c>
-      <c r="BB30" t="n">
+      <c r="BB30" t="inlineStr"/>
+      <c r="BC30" t="n">
         <v>1</v>
       </c>
-      <c r="BC30" t="inlineStr">
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE30" t="inlineStr">
         <is>
           <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
         </is>
       </c>
-      <c r="BD30" t="inlineStr">
+      <c r="BF30" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
       </c>
+      <c r="BG30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3917,6 +4954,7 @@
           <t>TTO-0016</t>
         </is>
       </c>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
         <v>16</v>
       </c>
@@ -3935,10 +4973,8 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G31" s="1" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
+      <c r="G31" t="n">
+        <v>780</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -3986,6 +5022,10 @@
           <t>TUNAPUNA/PIARCO</t>
         </is>
       </c>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -4001,22 +5041,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr"/>
+      <c r="AI31" t="inlineStr"/>
+      <c r="AJ31" t="inlineStr"/>
+      <c r="AK31" t="inlineStr"/>
+      <c r="AL31" t="inlineStr"/>
+      <c r="AM31" t="inlineStr"/>
+      <c r="AN31" t="inlineStr"/>
+      <c r="AO31" t="inlineStr"/>
+      <c r="AP31" t="inlineStr"/>
+      <c r="AQ31" t="inlineStr"/>
+      <c r="AR31" t="inlineStr"/>
+      <c r="AS31" t="inlineStr"/>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AU31" t="inlineStr"/>
+      <c r="AV31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr"/>
+      <c r="AX31" t="inlineStr"/>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr"/>
       <c r="BA31" t="n">
         <v>2</v>
       </c>
-      <c r="BB31" t="n">
+      <c r="BB31" t="inlineStr"/>
+      <c r="BC31" t="n">
         <v>1</v>
       </c>
-      <c r="BC31" t="inlineStr">
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE31" t="inlineStr">
         <is>
           <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
         </is>
       </c>
-      <c r="BD31" t="inlineStr">
+      <c r="BF31" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
       </c>
+      <c r="BG31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4024,6 +5099,7 @@
           <t>TTO-0016</t>
         </is>
       </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
         <v>16</v>
       </c>
@@ -4042,10 +5118,8 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G32" s="1" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
+      <c r="G32" t="n">
+        <v>780</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -4093,6 +5167,10 @@
           <t>TUNAPUNA/PIARCO</t>
         </is>
       </c>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -4108,22 +5186,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr"/>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr"/>
+      <c r="AJ32" t="inlineStr"/>
+      <c r="AK32" t="inlineStr"/>
+      <c r="AL32" t="inlineStr"/>
+      <c r="AM32" t="inlineStr"/>
+      <c r="AN32" t="inlineStr"/>
+      <c r="AO32" t="inlineStr"/>
+      <c r="AP32" t="inlineStr"/>
+      <c r="AQ32" t="inlineStr"/>
+      <c r="AR32" t="inlineStr"/>
+      <c r="AS32" t="inlineStr"/>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AU32" t="inlineStr"/>
+      <c r="AV32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr"/>
+      <c r="AX32" t="inlineStr"/>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr"/>
       <c r="BA32" t="n">
         <v>2</v>
       </c>
-      <c r="BB32" t="n">
+      <c r="BB32" t="inlineStr"/>
+      <c r="BC32" t="n">
         <v>1</v>
       </c>
-      <c r="BC32" t="inlineStr">
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE32" t="inlineStr">
         <is>
           <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
         </is>
       </c>
-      <c r="BD32" t="inlineStr">
+      <c r="BF32" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
       </c>
+      <c r="BG32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4131,6 +5244,7 @@
           <t>TTO-0016</t>
         </is>
       </c>
+      <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
         <v>16</v>
       </c>
@@ -4149,10 +5263,8 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G33" s="1" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
+      <c r="G33" t="n">
+        <v>780</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -4200,6 +5312,10 @@
           <t>TUNAPUNA/PIARCO</t>
         </is>
       </c>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -4215,22 +5331,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr"/>
+      <c r="AJ33" t="inlineStr"/>
+      <c r="AK33" t="inlineStr"/>
+      <c r="AL33" t="inlineStr"/>
+      <c r="AM33" t="inlineStr"/>
+      <c r="AN33" t="inlineStr"/>
+      <c r="AO33" t="inlineStr"/>
+      <c r="AP33" t="inlineStr"/>
+      <c r="AQ33" t="inlineStr"/>
+      <c r="AR33" t="inlineStr"/>
+      <c r="AS33" t="inlineStr"/>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AU33" t="inlineStr"/>
+      <c r="AV33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr"/>
+      <c r="AX33" t="inlineStr"/>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr"/>
       <c r="BA33" t="n">
         <v>2</v>
       </c>
-      <c r="BB33" t="n">
+      <c r="BB33" t="inlineStr"/>
+      <c r="BC33" t="n">
         <v>1</v>
       </c>
-      <c r="BC33" t="inlineStr">
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE33" t="inlineStr">
         <is>
           <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
         </is>
       </c>
-      <c r="BD33" t="inlineStr">
+      <c r="BF33" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
       </c>
+      <c r="BG33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4238,6 +5389,7 @@
           <t>TTO-0016</t>
         </is>
       </c>
+      <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
         <v>16</v>
       </c>
@@ -4256,10 +5408,8 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G34" s="1" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
+      <c r="G34" t="n">
+        <v>780</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -4307,6 +5457,10 @@
           <t>TUNAPUNA/PIARCO</t>
         </is>
       </c>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -4322,22 +5476,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr"/>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr"/>
+      <c r="AJ34" t="inlineStr"/>
+      <c r="AK34" t="inlineStr"/>
+      <c r="AL34" t="inlineStr"/>
+      <c r="AM34" t="inlineStr"/>
+      <c r="AN34" t="inlineStr"/>
+      <c r="AO34" t="inlineStr"/>
+      <c r="AP34" t="inlineStr"/>
+      <c r="AQ34" t="inlineStr"/>
+      <c r="AR34" t="inlineStr"/>
+      <c r="AS34" t="inlineStr"/>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AU34" t="inlineStr"/>
+      <c r="AV34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr"/>
+      <c r="AX34" t="inlineStr"/>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr"/>
       <c r="BA34" t="n">
         <v>2</v>
       </c>
-      <c r="BB34" t="n">
+      <c r="BB34" t="inlineStr"/>
+      <c r="BC34" t="n">
         <v>1</v>
       </c>
-      <c r="BC34" t="inlineStr">
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE34" t="inlineStr">
         <is>
           <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
         </is>
       </c>
-      <c r="BD34" t="inlineStr">
+      <c r="BF34" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
       </c>
+      <c r="BG34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4345,6 +5534,7 @@
           <t>TTO-0016</t>
         </is>
       </c>
+      <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
         <v>16</v>
       </c>
@@ -4363,10 +5553,8 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G35" s="1" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
+      <c r="G35" t="n">
+        <v>780</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -4414,6 +5602,10 @@
           <t>TUNAPUNA/PIARCO</t>
         </is>
       </c>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -4429,22 +5621,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr"/>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr"/>
+      <c r="AJ35" t="inlineStr"/>
+      <c r="AK35" t="inlineStr"/>
+      <c r="AL35" t="inlineStr"/>
+      <c r="AM35" t="inlineStr"/>
+      <c r="AN35" t="inlineStr"/>
+      <c r="AO35" t="inlineStr"/>
+      <c r="AP35" t="inlineStr"/>
+      <c r="AQ35" t="inlineStr"/>
+      <c r="AR35" t="inlineStr"/>
+      <c r="AS35" t="inlineStr"/>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AU35" t="inlineStr"/>
+      <c r="AV35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr"/>
+      <c r="AX35" t="inlineStr"/>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr"/>
       <c r="BA35" t="n">
         <v>2</v>
       </c>
-      <c r="BB35" t="n">
+      <c r="BB35" t="inlineStr"/>
+      <c r="BC35" t="n">
         <v>1</v>
       </c>
-      <c r="BC35" t="inlineStr">
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE35" t="inlineStr">
         <is>
           <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
         </is>
       </c>
-      <c r="BD35" t="inlineStr">
+      <c r="BF35" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
       </c>
+      <c r="BG35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4452,6 +5679,7 @@
           <t>TTO-0016</t>
         </is>
       </c>
+      <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
         <v>16</v>
       </c>
@@ -4470,10 +5698,8 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G36" s="1" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
+      <c r="G36" t="n">
+        <v>780</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -4521,6 +5747,10 @@
           <t>TUNAPUNA/PIARCO</t>
         </is>
       </c>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -4536,22 +5766,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr"/>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr"/>
+      <c r="AJ36" t="inlineStr"/>
+      <c r="AK36" t="inlineStr"/>
+      <c r="AL36" t="inlineStr"/>
+      <c r="AM36" t="inlineStr"/>
+      <c r="AN36" t="inlineStr"/>
+      <c r="AO36" t="inlineStr"/>
+      <c r="AP36" t="inlineStr"/>
+      <c r="AQ36" t="inlineStr"/>
+      <c r="AR36" t="inlineStr"/>
+      <c r="AS36" t="inlineStr"/>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AU36" t="inlineStr"/>
+      <c r="AV36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr"/>
+      <c r="AX36" t="inlineStr"/>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr"/>
       <c r="BA36" t="n">
         <v>2</v>
       </c>
-      <c r="BB36" t="n">
+      <c r="BB36" t="inlineStr"/>
+      <c r="BC36" t="n">
         <v>1</v>
       </c>
-      <c r="BC36" t="inlineStr">
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE36" t="inlineStr">
         <is>
           <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
         </is>
       </c>
-      <c r="BD36" t="inlineStr">
+      <c r="BF36" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
       </c>
+      <c r="BG36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4559,6 +5824,7 @@
           <t>TTO-0016</t>
         </is>
       </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
         <v>16</v>
       </c>
@@ -4577,10 +5843,8 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G37" s="1" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
+      <c r="G37" t="n">
+        <v>780</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -4628,6 +5892,10 @@
           <t>TUNAPUNA/PIARCO</t>
         </is>
       </c>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -4643,22 +5911,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="inlineStr"/>
+      <c r="AD37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr"/>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr"/>
+      <c r="AI37" t="inlineStr"/>
+      <c r="AJ37" t="inlineStr"/>
+      <c r="AK37" t="inlineStr"/>
+      <c r="AL37" t="inlineStr"/>
+      <c r="AM37" t="inlineStr"/>
+      <c r="AN37" t="inlineStr"/>
+      <c r="AO37" t="inlineStr"/>
+      <c r="AP37" t="inlineStr"/>
+      <c r="AQ37" t="inlineStr"/>
+      <c r="AR37" t="inlineStr"/>
+      <c r="AS37" t="inlineStr"/>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AU37" t="inlineStr"/>
+      <c r="AV37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr"/>
+      <c r="AX37" t="inlineStr"/>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr"/>
       <c r="BA37" t="n">
         <v>2</v>
       </c>
-      <c r="BB37" t="n">
+      <c r="BB37" t="inlineStr"/>
+      <c r="BC37" t="n">
         <v>1</v>
       </c>
-      <c r="BC37" t="inlineStr">
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE37" t="inlineStr">
         <is>
           <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
         </is>
       </c>
-      <c r="BD37" t="inlineStr">
+      <c r="BF37" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
       </c>
+      <c r="BG37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4666,6 +5969,7 @@
           <t>TTO-0016</t>
         </is>
       </c>
+      <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
         <v>16</v>
       </c>
@@ -4684,10 +5988,8 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G38" s="1" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
+      <c r="G38" t="n">
+        <v>780</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -4735,6 +6037,10 @@
           <t>TUNAPUNA/PIARCO</t>
         </is>
       </c>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -4750,22 +6056,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="inlineStr"/>
+      <c r="AD38" t="inlineStr"/>
+      <c r="AE38" t="inlineStr"/>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr"/>
+      <c r="AI38" t="inlineStr"/>
+      <c r="AJ38" t="inlineStr"/>
+      <c r="AK38" t="inlineStr"/>
+      <c r="AL38" t="inlineStr"/>
+      <c r="AM38" t="inlineStr"/>
+      <c r="AN38" t="inlineStr"/>
+      <c r="AO38" t="inlineStr"/>
+      <c r="AP38" t="inlineStr"/>
+      <c r="AQ38" t="inlineStr"/>
+      <c r="AR38" t="inlineStr"/>
+      <c r="AS38" t="inlineStr"/>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AU38" t="inlineStr"/>
+      <c r="AV38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr"/>
+      <c r="AX38" t="inlineStr"/>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr"/>
       <c r="BA38" t="n">
         <v>2</v>
       </c>
-      <c r="BB38" t="n">
+      <c r="BB38" t="inlineStr"/>
+      <c r="BC38" t="n">
         <v>1</v>
       </c>
-      <c r="BC38" t="inlineStr">
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE38" t="inlineStr">
         <is>
           <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
         </is>
       </c>
-      <c r="BD38" t="inlineStr">
+      <c r="BF38" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
       </c>
+      <c r="BG38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4773,6 +6114,7 @@
           <t>TTO-0016</t>
         </is>
       </c>
+      <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
         <v>16</v>
       </c>
@@ -4791,10 +6133,8 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G39" s="1" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
+      <c r="G39" t="n">
+        <v>780</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -4842,6 +6182,10 @@
           <t>TUNAPUNA/PIARCO</t>
         </is>
       </c>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -4857,22 +6201,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="inlineStr"/>
+      <c r="AD39" t="inlineStr"/>
+      <c r="AE39" t="inlineStr"/>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="inlineStr"/>
+      <c r="AI39" t="inlineStr"/>
+      <c r="AJ39" t="inlineStr"/>
+      <c r="AK39" t="inlineStr"/>
+      <c r="AL39" t="inlineStr"/>
+      <c r="AM39" t="inlineStr"/>
+      <c r="AN39" t="inlineStr"/>
+      <c r="AO39" t="inlineStr"/>
+      <c r="AP39" t="inlineStr"/>
+      <c r="AQ39" t="inlineStr"/>
+      <c r="AR39" t="inlineStr"/>
+      <c r="AS39" t="inlineStr"/>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AU39" t="inlineStr"/>
+      <c r="AV39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr"/>
+      <c r="AX39" t="inlineStr"/>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr"/>
       <c r="BA39" t="n">
         <v>2</v>
       </c>
-      <c r="BB39" t="n">
+      <c r="BB39" t="inlineStr"/>
+      <c r="BC39" t="n">
         <v>1</v>
       </c>
-      <c r="BC39" t="inlineStr">
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE39" t="inlineStr">
         <is>
           <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
         </is>
       </c>
-      <c r="BD39" t="inlineStr">
+      <c r="BF39" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
       </c>
+      <c r="BG39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4880,6 +6259,7 @@
           <t>TTO-0016</t>
         </is>
       </c>
+      <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
         <v>16</v>
       </c>
@@ -4898,10 +6278,8 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G40" s="1" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
+      <c r="G40" t="n">
+        <v>780</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -4949,6 +6327,10 @@
           <t>SANGRE GRANDE</t>
         </is>
       </c>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -4964,22 +6346,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="inlineStr"/>
+      <c r="AD40" t="inlineStr"/>
+      <c r="AE40" t="inlineStr"/>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="inlineStr"/>
+      <c r="AH40" t="inlineStr"/>
+      <c r="AI40" t="inlineStr"/>
+      <c r="AJ40" t="inlineStr"/>
+      <c r="AK40" t="inlineStr"/>
+      <c r="AL40" t="inlineStr"/>
+      <c r="AM40" t="inlineStr"/>
+      <c r="AN40" t="inlineStr"/>
+      <c r="AO40" t="inlineStr"/>
+      <c r="AP40" t="inlineStr"/>
+      <c r="AQ40" t="inlineStr"/>
+      <c r="AR40" t="inlineStr"/>
+      <c r="AS40" t="inlineStr"/>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AU40" t="inlineStr"/>
+      <c r="AV40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr"/>
+      <c r="AX40" t="inlineStr"/>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr"/>
       <c r="BA40" t="n">
         <v>2</v>
       </c>
-      <c r="BB40" t="n">
+      <c r="BB40" t="inlineStr"/>
+      <c r="BC40" t="n">
         <v>1</v>
       </c>
-      <c r="BC40" t="inlineStr">
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE40" t="inlineStr">
         <is>
           <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
         </is>
       </c>
-      <c r="BD40" t="inlineStr">
+      <c r="BF40" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
       </c>
+      <c r="BG40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4987,6 +6404,7 @@
           <t>TTO-0016</t>
         </is>
       </c>
+      <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
         <v>16</v>
       </c>
@@ -5005,10 +6423,8 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G41" s="1" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
+      <c r="G41" t="n">
+        <v>780</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -5056,6 +6472,10 @@
           <t>SANGRE GRANDE</t>
         </is>
       </c>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -5071,22 +6491,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr"/>
+      <c r="AC41" t="inlineStr"/>
+      <c r="AD41" t="inlineStr"/>
+      <c r="AE41" t="inlineStr"/>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="inlineStr"/>
+      <c r="AI41" t="inlineStr"/>
+      <c r="AJ41" t="inlineStr"/>
+      <c r="AK41" t="inlineStr"/>
+      <c r="AL41" t="inlineStr"/>
+      <c r="AM41" t="inlineStr"/>
+      <c r="AN41" t="inlineStr"/>
+      <c r="AO41" t="inlineStr"/>
+      <c r="AP41" t="inlineStr"/>
+      <c r="AQ41" t="inlineStr"/>
+      <c r="AR41" t="inlineStr"/>
+      <c r="AS41" t="inlineStr"/>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AU41" t="inlineStr"/>
+      <c r="AV41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr"/>
+      <c r="AX41" t="inlineStr"/>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr"/>
       <c r="BA41" t="n">
         <v>2</v>
       </c>
-      <c r="BB41" t="n">
+      <c r="BB41" t="inlineStr"/>
+      <c r="BC41" t="n">
         <v>1</v>
       </c>
-      <c r="BC41" t="inlineStr">
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE41" t="inlineStr">
         <is>
           <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
         </is>
       </c>
-      <c r="BD41" t="inlineStr">
+      <c r="BF41" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
       </c>
+      <c r="BG41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5094,6 +6549,7 @@
           <t>TTO-0016</t>
         </is>
       </c>
+      <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
         <v>16</v>
       </c>
@@ -5112,10 +6568,8 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G42" s="1" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
+      <c r="G42" t="n">
+        <v>780</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -5163,6 +6617,10 @@
           <t>SANGRE GRANDE</t>
         </is>
       </c>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -5178,22 +6636,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="inlineStr"/>
+      <c r="AD42" t="inlineStr"/>
+      <c r="AE42" t="inlineStr"/>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="inlineStr"/>
+      <c r="AH42" t="inlineStr"/>
+      <c r="AI42" t="inlineStr"/>
+      <c r="AJ42" t="inlineStr"/>
+      <c r="AK42" t="inlineStr"/>
+      <c r="AL42" t="inlineStr"/>
+      <c r="AM42" t="inlineStr"/>
+      <c r="AN42" t="inlineStr"/>
+      <c r="AO42" t="inlineStr"/>
+      <c r="AP42" t="inlineStr"/>
+      <c r="AQ42" t="inlineStr"/>
+      <c r="AR42" t="inlineStr"/>
+      <c r="AS42" t="inlineStr"/>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AU42" t="inlineStr"/>
+      <c r="AV42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr"/>
+      <c r="AX42" t="inlineStr"/>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr"/>
       <c r="BA42" t="n">
         <v>2</v>
       </c>
-      <c r="BB42" t="n">
+      <c r="BB42" t="inlineStr"/>
+      <c r="BC42" t="n">
         <v>1</v>
       </c>
-      <c r="BC42" t="inlineStr">
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE42" t="inlineStr">
         <is>
           <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
         </is>
       </c>
-      <c r="BD42" t="inlineStr">
+      <c r="BF42" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
       </c>
+      <c r="BG42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5201,6 +6694,7 @@
           <t>TTO-0016</t>
         </is>
       </c>
+      <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
         <v>16</v>
       </c>
@@ -5219,10 +6713,8 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G43" s="1" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
+      <c r="G43" t="n">
+        <v>780</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -5270,6 +6762,10 @@
           <t>SANGRE GRANDE</t>
         </is>
       </c>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -5285,22 +6781,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
+      <c r="AC43" t="inlineStr"/>
+      <c r="AD43" t="inlineStr"/>
+      <c r="AE43" t="inlineStr"/>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="inlineStr"/>
+      <c r="AH43" t="inlineStr"/>
+      <c r="AI43" t="inlineStr"/>
+      <c r="AJ43" t="inlineStr"/>
+      <c r="AK43" t="inlineStr"/>
+      <c r="AL43" t="inlineStr"/>
+      <c r="AM43" t="inlineStr"/>
+      <c r="AN43" t="inlineStr"/>
+      <c r="AO43" t="inlineStr"/>
+      <c r="AP43" t="inlineStr"/>
+      <c r="AQ43" t="inlineStr"/>
+      <c r="AR43" t="inlineStr"/>
+      <c r="AS43" t="inlineStr"/>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AU43" t="inlineStr"/>
+      <c r="AV43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr"/>
+      <c r="AX43" t="inlineStr"/>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr"/>
       <c r="BA43" t="n">
         <v>2</v>
       </c>
-      <c r="BB43" t="n">
+      <c r="BB43" t="inlineStr"/>
+      <c r="BC43" t="n">
         <v>1</v>
       </c>
-      <c r="BC43" t="inlineStr">
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE43" t="inlineStr">
         <is>
           <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
         </is>
       </c>
-      <c r="BD43" t="inlineStr">
+      <c r="BF43" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
       </c>
+      <c r="BG43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5308,6 +6839,7 @@
           <t>TTO-0016</t>
         </is>
       </c>
+      <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
         <v>16</v>
       </c>
@@ -5326,10 +6858,8 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G44" s="1" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
+      <c r="G44" t="n">
+        <v>780</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -5377,6 +6907,10 @@
           <t>SANGRE GRANDE</t>
         </is>
       </c>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -5392,22 +6926,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr"/>
+      <c r="AC44" t="inlineStr"/>
+      <c r="AD44" t="inlineStr"/>
+      <c r="AE44" t="inlineStr"/>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="inlineStr"/>
+      <c r="AH44" t="inlineStr"/>
+      <c r="AI44" t="inlineStr"/>
+      <c r="AJ44" t="inlineStr"/>
+      <c r="AK44" t="inlineStr"/>
+      <c r="AL44" t="inlineStr"/>
+      <c r="AM44" t="inlineStr"/>
+      <c r="AN44" t="inlineStr"/>
+      <c r="AO44" t="inlineStr"/>
+      <c r="AP44" t="inlineStr"/>
+      <c r="AQ44" t="inlineStr"/>
+      <c r="AR44" t="inlineStr"/>
+      <c r="AS44" t="inlineStr"/>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AU44" t="inlineStr"/>
+      <c r="AV44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr"/>
+      <c r="AX44" t="inlineStr"/>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr"/>
       <c r="BA44" t="n">
         <v>2</v>
       </c>
-      <c r="BB44" t="n">
+      <c r="BB44" t="inlineStr"/>
+      <c r="BC44" t="n">
         <v>1</v>
       </c>
-      <c r="BC44" t="inlineStr">
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE44" t="inlineStr">
         <is>
           <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
         </is>
       </c>
-      <c r="BD44" t="inlineStr">
+      <c r="BF44" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
       </c>
+      <c r="BG44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5415,6 +6984,7 @@
           <t>TTO-0016</t>
         </is>
       </c>
+      <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
         <v>16</v>
       </c>
@@ -5433,10 +7003,8 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G45" s="1" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
+      <c r="G45" t="n">
+        <v>780</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -5484,6 +7052,10 @@
           <t>SANGRE GRANDE</t>
         </is>
       </c>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -5499,22 +7071,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr"/>
+      <c r="AB45" t="inlineStr"/>
+      <c r="AC45" t="inlineStr"/>
+      <c r="AD45" t="inlineStr"/>
+      <c r="AE45" t="inlineStr"/>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="inlineStr"/>
+      <c r="AH45" t="inlineStr"/>
+      <c r="AI45" t="inlineStr"/>
+      <c r="AJ45" t="inlineStr"/>
+      <c r="AK45" t="inlineStr"/>
+      <c r="AL45" t="inlineStr"/>
+      <c r="AM45" t="inlineStr"/>
+      <c r="AN45" t="inlineStr"/>
+      <c r="AO45" t="inlineStr"/>
+      <c r="AP45" t="inlineStr"/>
+      <c r="AQ45" t="inlineStr"/>
+      <c r="AR45" t="inlineStr"/>
+      <c r="AS45" t="inlineStr"/>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AU45" t="inlineStr"/>
+      <c r="AV45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr"/>
+      <c r="AX45" t="inlineStr"/>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr"/>
       <c r="BA45" t="n">
         <v>2</v>
       </c>
-      <c r="BB45" t="n">
+      <c r="BB45" t="inlineStr"/>
+      <c r="BC45" t="n">
         <v>1</v>
       </c>
-      <c r="BC45" t="inlineStr">
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE45" t="inlineStr">
         <is>
           <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
         </is>
       </c>
-      <c r="BD45" t="inlineStr">
+      <c r="BF45" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
       </c>
+      <c r="BG45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5522,6 +7129,7 @@
           <t>TTO-0016</t>
         </is>
       </c>
+      <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
         <v>16</v>
       </c>
@@ -5540,10 +7148,8 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G46" s="1" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
+      <c r="G46" t="n">
+        <v>780</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -5591,6 +7197,10 @@
           <t>SANGRE GRANDE</t>
         </is>
       </c>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -5606,22 +7216,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr"/>
+      <c r="AB46" t="inlineStr"/>
+      <c r="AC46" t="inlineStr"/>
+      <c r="AD46" t="inlineStr"/>
+      <c r="AE46" t="inlineStr"/>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr"/>
+      <c r="AI46" t="inlineStr"/>
+      <c r="AJ46" t="inlineStr"/>
+      <c r="AK46" t="inlineStr"/>
+      <c r="AL46" t="inlineStr"/>
+      <c r="AM46" t="inlineStr"/>
+      <c r="AN46" t="inlineStr"/>
+      <c r="AO46" t="inlineStr"/>
+      <c r="AP46" t="inlineStr"/>
+      <c r="AQ46" t="inlineStr"/>
+      <c r="AR46" t="inlineStr"/>
+      <c r="AS46" t="inlineStr"/>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AU46" t="inlineStr"/>
+      <c r="AV46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr"/>
+      <c r="AX46" t="inlineStr"/>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr"/>
       <c r="BA46" t="n">
         <v>2</v>
       </c>
-      <c r="BB46" t="n">
+      <c r="BB46" t="inlineStr"/>
+      <c r="BC46" t="n">
         <v>1</v>
       </c>
-      <c r="BC46" t="inlineStr">
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE46" t="inlineStr">
         <is>
           <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
         </is>
       </c>
-      <c r="BD46" t="inlineStr">
+      <c r="BF46" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
       </c>
+      <c r="BG46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5629,6 +7274,7 @@
           <t>TTO-0016</t>
         </is>
       </c>
+      <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
         <v>16</v>
       </c>
@@ -5647,10 +7293,8 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G47" s="1" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
+      <c r="G47" t="n">
+        <v>780</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -5698,6 +7342,10 @@
           <t>SANGRE GRANDE</t>
         </is>
       </c>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -5713,22 +7361,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr"/>
+      <c r="AB47" t="inlineStr"/>
+      <c r="AC47" t="inlineStr"/>
+      <c r="AD47" t="inlineStr"/>
+      <c r="AE47" t="inlineStr"/>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="inlineStr"/>
+      <c r="AI47" t="inlineStr"/>
+      <c r="AJ47" t="inlineStr"/>
+      <c r="AK47" t="inlineStr"/>
+      <c r="AL47" t="inlineStr"/>
+      <c r="AM47" t="inlineStr"/>
+      <c r="AN47" t="inlineStr"/>
+      <c r="AO47" t="inlineStr"/>
+      <c r="AP47" t="inlineStr"/>
+      <c r="AQ47" t="inlineStr"/>
+      <c r="AR47" t="inlineStr"/>
+      <c r="AS47" t="inlineStr"/>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AU47" t="inlineStr"/>
+      <c r="AV47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr"/>
+      <c r="AX47" t="inlineStr"/>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr"/>
       <c r="BA47" t="n">
         <v>2</v>
       </c>
-      <c r="BB47" t="n">
+      <c r="BB47" t="inlineStr"/>
+      <c r="BC47" t="n">
         <v>1</v>
       </c>
-      <c r="BC47" t="inlineStr">
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE47" t="inlineStr">
         <is>
           <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
         </is>
       </c>
-      <c r="BD47" t="inlineStr">
+      <c r="BF47" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
       </c>
+      <c r="BG47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5736,6 +7419,7 @@
           <t>TTO-0016</t>
         </is>
       </c>
+      <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
         <v>16</v>
       </c>
@@ -5754,10 +7438,8 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G48" s="1" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
+      <c r="G48" t="n">
+        <v>780</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -5805,6 +7487,10 @@
           <t>SANGRE GRANDE</t>
         </is>
       </c>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -5820,22 +7506,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr"/>
+      <c r="AB48" t="inlineStr"/>
+      <c r="AC48" t="inlineStr"/>
+      <c r="AD48" t="inlineStr"/>
+      <c r="AE48" t="inlineStr"/>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="inlineStr"/>
+      <c r="AH48" t="inlineStr"/>
+      <c r="AI48" t="inlineStr"/>
+      <c r="AJ48" t="inlineStr"/>
+      <c r="AK48" t="inlineStr"/>
+      <c r="AL48" t="inlineStr"/>
+      <c r="AM48" t="inlineStr"/>
+      <c r="AN48" t="inlineStr"/>
+      <c r="AO48" t="inlineStr"/>
+      <c r="AP48" t="inlineStr"/>
+      <c r="AQ48" t="inlineStr"/>
+      <c r="AR48" t="inlineStr"/>
+      <c r="AS48" t="inlineStr"/>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AU48" t="inlineStr"/>
+      <c r="AV48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr"/>
+      <c r="AX48" t="inlineStr"/>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr"/>
       <c r="BA48" t="n">
         <v>2</v>
       </c>
-      <c r="BB48" t="n">
+      <c r="BB48" t="inlineStr"/>
+      <c r="BC48" t="n">
         <v>1</v>
       </c>
-      <c r="BC48" t="inlineStr">
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE48" t="inlineStr">
         <is>
           <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
         </is>
       </c>
-      <c r="BD48" t="inlineStr">
+      <c r="BF48" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
       </c>
+      <c r="BG48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5843,6 +7564,7 @@
           <t>TTO-0016</t>
         </is>
       </c>
+      <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
         <v>16</v>
       </c>
@@ -5861,10 +7583,8 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G49" s="1" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
+      <c r="G49" t="n">
+        <v>780</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -5912,6 +7632,10 @@
           <t>SANGRE GRANDE</t>
         </is>
       </c>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -5927,22 +7651,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr"/>
+      <c r="AB49" t="inlineStr"/>
+      <c r="AC49" t="inlineStr"/>
+      <c r="AD49" t="inlineStr"/>
+      <c r="AE49" t="inlineStr"/>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="inlineStr"/>
+      <c r="AH49" t="inlineStr"/>
+      <c r="AI49" t="inlineStr"/>
+      <c r="AJ49" t="inlineStr"/>
+      <c r="AK49" t="inlineStr"/>
+      <c r="AL49" t="inlineStr"/>
+      <c r="AM49" t="inlineStr"/>
+      <c r="AN49" t="inlineStr"/>
+      <c r="AO49" t="inlineStr"/>
+      <c r="AP49" t="inlineStr"/>
+      <c r="AQ49" t="inlineStr"/>
+      <c r="AR49" t="inlineStr"/>
+      <c r="AS49" t="inlineStr"/>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AU49" t="inlineStr"/>
+      <c r="AV49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr"/>
+      <c r="AX49" t="inlineStr"/>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr"/>
       <c r="BA49" t="n">
         <v>2</v>
       </c>
-      <c r="BB49" t="n">
+      <c r="BB49" t="inlineStr"/>
+      <c r="BC49" t="n">
         <v>1</v>
       </c>
-      <c r="BC49" t="inlineStr">
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE49" t="inlineStr">
         <is>
           <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
         </is>
       </c>
-      <c r="BD49" t="inlineStr">
+      <c r="BF49" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
       </c>
+      <c r="BG49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5950,6 +7709,7 @@
           <t>TTO-0016</t>
         </is>
       </c>
+      <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
         <v>16</v>
       </c>
@@ -5968,10 +7728,8 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G50" s="1" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
+      <c r="G50" t="n">
+        <v>780</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -6019,6 +7777,10 @@
           <t>SANGRE GRANDE</t>
         </is>
       </c>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -6034,22 +7796,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr"/>
+      <c r="AB50" t="inlineStr"/>
+      <c r="AC50" t="inlineStr"/>
+      <c r="AD50" t="inlineStr"/>
+      <c r="AE50" t="inlineStr"/>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="inlineStr"/>
+      <c r="AH50" t="inlineStr"/>
+      <c r="AI50" t="inlineStr"/>
+      <c r="AJ50" t="inlineStr"/>
+      <c r="AK50" t="inlineStr"/>
+      <c r="AL50" t="inlineStr"/>
+      <c r="AM50" t="inlineStr"/>
+      <c r="AN50" t="inlineStr"/>
+      <c r="AO50" t="inlineStr"/>
+      <c r="AP50" t="inlineStr"/>
+      <c r="AQ50" t="inlineStr"/>
+      <c r="AR50" t="inlineStr"/>
+      <c r="AS50" t="inlineStr"/>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AU50" t="inlineStr"/>
+      <c r="AV50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr"/>
+      <c r="AX50" t="inlineStr"/>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr"/>
       <c r="BA50" t="n">
         <v>2</v>
       </c>
-      <c r="BB50" t="n">
+      <c r="BB50" t="inlineStr"/>
+      <c r="BC50" t="n">
         <v>1</v>
       </c>
-      <c r="BC50" t="inlineStr">
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE50" t="inlineStr">
         <is>
           <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
         </is>
       </c>
-      <c r="BD50" t="inlineStr">
+      <c r="BF50" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
       </c>
+      <c r="BG50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6057,6 +7854,7 @@
           <t>TTO-0016</t>
         </is>
       </c>
+      <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
         <v>16</v>
       </c>
@@ -6075,10 +7873,8 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G51" s="1" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
+      <c r="G51" t="n">
+        <v>780</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -6126,6 +7922,10 @@
           <t>SAN JUAN-LAVENTILLE</t>
         </is>
       </c>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -6141,22 +7941,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr"/>
+      <c r="AB51" t="inlineStr"/>
+      <c r="AC51" t="inlineStr"/>
+      <c r="AD51" t="inlineStr"/>
+      <c r="AE51" t="inlineStr"/>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="inlineStr"/>
+      <c r="AH51" t="inlineStr"/>
+      <c r="AI51" t="inlineStr"/>
+      <c r="AJ51" t="inlineStr"/>
+      <c r="AK51" t="inlineStr"/>
+      <c r="AL51" t="inlineStr"/>
+      <c r="AM51" t="inlineStr"/>
+      <c r="AN51" t="inlineStr"/>
+      <c r="AO51" t="inlineStr"/>
+      <c r="AP51" t="inlineStr"/>
+      <c r="AQ51" t="inlineStr"/>
+      <c r="AR51" t="inlineStr"/>
+      <c r="AS51" t="inlineStr"/>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AU51" t="inlineStr"/>
+      <c r="AV51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr"/>
+      <c r="AX51" t="inlineStr"/>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr"/>
       <c r="BA51" t="n">
         <v>2</v>
       </c>
-      <c r="BB51" t="n">
+      <c r="BB51" t="inlineStr"/>
+      <c r="BC51" t="n">
         <v>1</v>
       </c>
-      <c r="BC51" t="inlineStr">
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE51" t="inlineStr">
         <is>
           <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
         </is>
       </c>
-      <c r="BD51" t="inlineStr">
+      <c r="BF51" t="inlineStr">
         <is>
           <t>https://www.mowt.gov.tt/Divisions/Highways-Division/Projects/Valencia-to-Toco-Roadway</t>
         </is>
       </c>
+      <c r="BG51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6164,6 +7999,7 @@
           <t>TTO-0017</t>
         </is>
       </c>
+      <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
         <v>17</v>
       </c>
@@ -6182,10 +8018,8 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G52" s="1" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
+      <c r="G52" t="n">
+        <v>780</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -6233,6 +8067,10 @@
           <t>COUVA-TABAQUITE-TALPARO</t>
         </is>
       </c>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -6248,23 +8086,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr"/>
+      <c r="AC52" t="inlineStr"/>
+      <c r="AD52" t="inlineStr"/>
+      <c r="AE52" t="inlineStr"/>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="inlineStr"/>
+      <c r="AH52" t="inlineStr"/>
+      <c r="AI52" t="inlineStr"/>
+      <c r="AJ52" t="inlineStr"/>
+      <c r="AK52" t="inlineStr"/>
+      <c r="AL52" t="inlineStr"/>
+      <c r="AM52" t="inlineStr"/>
+      <c r="AN52" t="inlineStr"/>
+      <c r="AO52" t="inlineStr"/>
+      <c r="AP52" t="inlineStr"/>
+      <c r="AQ52" t="inlineStr"/>
+      <c r="AR52" t="inlineStr"/>
+      <c r="AS52" t="inlineStr"/>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AU52" t="inlineStr"/>
+      <c r="AV52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr"/>
+      <c r="AX52" t="inlineStr"/>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr"/>
       <c r="BA52" t="n">
         <v>2</v>
       </c>
-      <c r="BB52" t="n">
+      <c r="BB52" t="inlineStr"/>
+      <c r="BC52" t="n">
         <v>1</v>
       </c>
-      <c r="BC52" t="inlineStr">
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE52" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Brian_Lara_Cricket_Academy</t>
         </is>
       </c>
-      <c r="BD52" t="inlineStr">
+      <c r="BF52" t="inlineStr">
         <is>
           <t>https://revanellis.com/chinas-engagement-with-trinidad-and-tobago</t>
         </is>
       </c>
-      <c r="BE52" t="inlineStr">
+      <c r="BG52" t="inlineStr">
         <is>
           <t>https://udecott.com/projects/brian-lara-cricket-academy/</t>
         </is>

--- a/data/sources/countries/trinidad_and_tobago.xlsx
+++ b/data/sources/countries/trinidad_and_tobago.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Acquisition from Talisman Energy of 100% of Talisman Trinidad Ltd., holder of a 25% working interest in the Block 2(c) production sharing contract, through the CNOOC-Sinopec joint venture Chaoyang Petroleum.</t>
+          <t>Acquisition from Talisman Energy of 100% of Talisman Trinidad Ltd., holder of a 25% working interest in the Block 2(c).</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Arima Hospital, built by China Railway with a China Exim Bank loan of RMB 802,512,402 (approx. USD 120M). Not to be confused with the Port of Spain General Hospital.</t>
+          <t>Arima Hospital, built by China Railway with a China Exim Bank loan of RMB 802,512,402 (approx. USD 120M).</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>South terminal of Piarco International Airport, delivered by SCG International (Caribbean) ahead of the 2009 Summit of the Americas.</t>
+          <t>South terminal of Piarco International Airport, delivered by SCG International (Caribbean) ahead of the 2009 Summit of.</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>National Cycling Centre velodrome and Couva Aquatic Centre, built by Shanghai Construction Group as part of a six-facility national sporting programme backed by an USD 85M China Exim preferential buyer's credit.</t>
+          <t>National Cycling Centre velodrome and Couva Aquatic Centre, built by Shanghai Construction Group as part of a.</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Malabar wastewater treatment plant and collection system (40,000 m3/day), awarded to Sinohydro in November 2014 and operational since July 2019.</t>
+          <t>Malabar wastewater treatment plant and collection system (40,000 m3/day), awarded to Sinohydro in November 2014 and.</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Phoenix Park Industrial Estate at Point Lisas, developed by BCEG with a China Exim Bank concessional loan of RMB 688,347,000. First Belt and Road project in the Caribbean.</t>
+          <t>Phoenix Park Industrial Estate at Point Lisas, developed by BCEG with a China Exim Bank concessional loan of RMB 688,</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Chinese firms Summit Luggage Co. and Docare Quanzhou Hygienic Product establishing operations at the Phoenix Park Industrial Estate. Direct investment, distinct from the estate itself.</t>
+          <t>Chinese firms Summit Luggage Co. and Docare Quanzhou Hygienic Product establishing operations at the Phoenix Park.</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Award of deepwater blocks TTDAA 24 and TTDAA 25 in the north-west of the Exclusive Economic Zone to CNOOC International, following the 2025 Deepwater Bid Round. Production sharing contracts still to be executed.</t>
+          <t>Award of deepwater blocks TTDAA 24 and TTDAA 25 in the north-west of the Exclusive Economic Zone to CNOOC International,</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Curepe interchange, awarded by NIDCO in August 2017 to a consortium led by China Railway Construction (Caribbean) and commissioned in June 2020.</t>
+          <t>Curepe interchange, awarded by NIDCO in August 2017 to a consortium led by China Railway Construction (Caribbean) and...</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>New 268,000 m2 terminal at A.N.R. Robinson International Airport, Tobago, built by China Railway Construction (Caribbean); works from July 2020 to practical completion in 2025.</t>
+          <t>New 268,000 m2 terminal at A.N.R. Robinson International Airport, Tobago, built by China Railway Construction.</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Acquisition of a 10% interest in Atlantic LNG (Train 1) from GDF Suez by the Chinese sovereign wealth fund CIC. Holding period 2011-2023.</t>
+          <t>Acquisition of a 10% interest in Atlantic LNG (Train 1) from GDF Suez by the Chinese sovereign wealth fund CIC.</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
